--- a/input_processing/clean_excel_files_PL/reg_retirement.xlsx
+++ b/input_processing/clean_excel_files_PL/reg_retirement.xlsx
@@ -117,10 +117,10 @@
     <t>Elig_pen_L1</t>
   </si>
   <si>
-    <t>Deh_c4_Medium</t>
-  </si>
-  <si>
-    <t>Deh_c4_Low</t>
+    <t>Deh_c4_Medium_L1</t>
+  </si>
+  <si>
+    <t>Deh_c4_Low_L1</t>
   </si>
   <si>
     <t>Reached_Retirement_Age</t>
@@ -394,7 +394,7 @@
         <v>17</v>
       </c>
       <c r="B5" s="1">
-        <v>0.26196456738157892</v>
+        <v>0.26196696547855247</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
@@ -402,7 +402,7 @@
         <v>24</v>
       </c>
       <c r="F5" s="1">
-        <v>1240.8086862163718</v>
+        <v>1240.9105993132525</v>
       </c>
     </row>
     <row r="6">
@@ -418,7 +418,7 @@
         <v>25</v>
       </c>
       <c r="F6" s="1">
-        <v>-2946688.6560477703</v>
+        <v>-2946679.0813785391</v>
       </c>
     </row>
     <row r="7">
@@ -474,7 +474,7 @@
         <v>17</v>
       </c>
       <c r="B11" s="1">
-        <v>0.31439927351053842</v>
+        <v>0.31439851395844831</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
@@ -482,7 +482,7 @@
         <v>24</v>
       </c>
       <c r="F11" s="1">
-        <v>3206.7261414411896</v>
+        <v>3207.6384773164709</v>
       </c>
     </row>
     <row r="12">
@@ -498,7 +498,7 @@
         <v>25</v>
       </c>
       <c r="F12" s="1">
-        <v>-7289843.6198002826</v>
+        <v>-7289851.6959526902</v>
       </c>
     </row>
   </sheetData>
@@ -586,70 +586,70 @@
         <v>28</v>
       </c>
       <c r="B2" s="1">
-        <v>-0.067480795944987321</v>
+        <v>-0.067465744422188487</v>
       </c>
       <c r="C2" s="1">
-        <v>0.0054687072782147053</v>
+        <v>0.0054687832340283293</v>
       </c>
       <c r="D2" s="1">
-        <v>-0.00027905143859019866</v>
+        <v>-0.00027860691504998265</v>
       </c>
       <c r="E2" s="1">
-        <v>1.7730545944684027e-06</v>
+        <v>1.7696484818866546e-06</v>
       </c>
       <c r="F2" s="1">
-        <v>-0.0043432813474923266</v>
+        <v>-0.0043438490856059645</v>
       </c>
       <c r="G2" s="1">
-        <v>-0.0035172900119950475</v>
+        <v>-0.0035177170903658763</v>
       </c>
       <c r="H2" s="1">
-        <v>-0.00045403456467682144</v>
+        <v>-0.00045489746242027872</v>
       </c>
       <c r="I2" s="1">
-        <v>-0.00062862017784685365</v>
+        <v>-0.00062948148366442349</v>
       </c>
       <c r="J2" s="1">
-        <v>0.0024207726028084727</v>
+        <v>0.0024201257037271876</v>
       </c>
       <c r="K2" s="1">
-        <v>0.00029269195668616169</v>
+        <v>0.00029283490894639478</v>
       </c>
       <c r="L2" s="1">
-        <v>-0.00012708938582782503</v>
+        <v>-0.00012965564297623769</v>
       </c>
       <c r="M2" s="1">
-        <v>-0.0010784240879178845</v>
+        <v>-0.0010800088675685963</v>
       </c>
       <c r="N2" s="1">
-        <v>-0.00066412106336970677</v>
+        <v>-0.00066559996694138266</v>
       </c>
       <c r="O2" s="1">
-        <v>-0.0014591975159760932</v>
+        <v>-0.001460569101181516</v>
       </c>
       <c r="P2" s="1">
-        <v>-0.00088671027620200959</v>
+        <v>-0.00088696305807333287</v>
       </c>
       <c r="Q2" s="1">
-        <v>-0.00031995136502455698</v>
+        <v>-0.00032002508144550251</v>
       </c>
       <c r="R2" s="1">
-        <v>0.00020488079719342038</v>
+        <v>0.00020491099749257464</v>
       </c>
       <c r="S2" s="1">
-        <v>0.00011891873370873589</v>
+        <v>0.00011878012526927322</v>
       </c>
       <c r="T2" s="1">
-        <v>0.00010815508494538728</v>
+        <v>0.00010850047922327704</v>
       </c>
       <c r="U2" s="1">
-        <v>-5.9471605398852103e-05</v>
+        <v>-5.9472437166146412e-05</v>
       </c>
       <c r="V2" s="1">
-        <v>0.00067779885389898783</v>
+        <v>0.00067759831483548121</v>
       </c>
       <c r="W2" s="1">
-        <v>0.0092155366467176481</v>
+        <v>0.0092038696369052819</v>
       </c>
     </row>
     <row r="3">
@@ -657,70 +657,70 @@
         <v>29</v>
       </c>
       <c r="B3" s="1">
-        <v>-0.0023637029514838657</v>
+        <v>-0.0023540339682555519</v>
       </c>
       <c r="C3" s="1">
-        <v>-0.00027905143859019866</v>
+        <v>-0.00027860691504998265</v>
       </c>
       <c r="D3" s="1">
-        <v>0.006156805964458778</v>
+        <v>0.0061567829178601763</v>
       </c>
       <c r="E3" s="1">
-        <v>-4.7521810104944953e-05</v>
+        <v>-4.7522021784917982e-05</v>
       </c>
       <c r="F3" s="1">
-        <v>-0.0017290735104626938</v>
+        <v>-0.0017293520164615309</v>
       </c>
       <c r="G3" s="1">
-        <v>-0.0025644436865721043</v>
+        <v>-0.0025646656809372448</v>
       </c>
       <c r="H3" s="1">
-        <v>-0.00036875802923581197</v>
+        <v>-0.00037785414271208906</v>
       </c>
       <c r="I3" s="1">
-        <v>0.00019750613892446922</v>
+        <v>0.00018875802709519135</v>
       </c>
       <c r="J3" s="1">
-        <v>-0.0042197139235300718</v>
+        <v>-0.0042198587556691453</v>
       </c>
       <c r="K3" s="1">
-        <v>-0.00024242926528108763</v>
+        <v>-0.00024203093231952091</v>
       </c>
       <c r="L3" s="1">
-        <v>-0.00010698817308102404</v>
+        <v>-0.00010745327257397769</v>
       </c>
       <c r="M3" s="1">
-        <v>-0.0004992319139945009</v>
+        <v>-0.00049987203046672479</v>
       </c>
       <c r="N3" s="1">
-        <v>-0.00062559994210271974</v>
+        <v>-0.00062692334473433975</v>
       </c>
       <c r="O3" s="1">
-        <v>-0.0004470597490751349</v>
+        <v>-0.00045134032412479791</v>
       </c>
       <c r="P3" s="1">
-        <v>-0.00081617103811412045</v>
+        <v>-0.00081655362378963564</v>
       </c>
       <c r="Q3" s="1">
-        <v>0.00022777525906596957</v>
+        <v>0.00022762542451128243</v>
       </c>
       <c r="R3" s="1">
-        <v>-6.2686421124072411e-05</v>
+        <v>-6.2739331759362194e-05</v>
       </c>
       <c r="S3" s="1">
-        <v>-1.1250208357280189e-05</v>
+        <v>-1.136353169683274e-05</v>
       </c>
       <c r="T3" s="1">
-        <v>0.00023156269370499041</v>
+        <v>0.00023124277766027948</v>
       </c>
       <c r="U3" s="1">
-        <v>-4.5586323035425036e-05</v>
+        <v>-4.5637073072948148e-05</v>
       </c>
       <c r="V3" s="1">
-        <v>0.00027214616557069693</v>
+        <v>0.00027232946578940875</v>
       </c>
       <c r="W3" s="1">
-        <v>-0.19270693019356422</v>
+        <v>-0.19269498968705623</v>
       </c>
     </row>
     <row r="4">
@@ -728,70 +728,70 @@
         <v>30</v>
       </c>
       <c r="B4" s="1">
-        <v>0.00031793518067315795</v>
+        <v>0.00031782974609182222</v>
       </c>
       <c r="C4" s="1">
-        <v>1.7730545944684027e-06</v>
+        <v>1.7696484818866546e-06</v>
       </c>
       <c r="D4" s="1">
-        <v>-4.7521810104944953e-05</v>
+        <v>-4.7522021784917982e-05</v>
       </c>
       <c r="E4" s="1">
-        <v>3.6894283211923209e-07</v>
+        <v>3.6894713902192966e-07</v>
       </c>
       <c r="F4" s="1">
-        <v>1.3579336350247199e-05</v>
+        <v>1.3581998461224909e-05</v>
       </c>
       <c r="G4" s="1">
-        <v>1.9346492382057382e-05</v>
+        <v>1.9348624443621138e-05</v>
       </c>
       <c r="H4" s="1">
-        <v>3.0551793969262053e-06</v>
+        <v>3.1222932744982617e-06</v>
       </c>
       <c r="I4" s="1">
-        <v>-1.6752916890906602e-06</v>
+        <v>-1.6103820858560437e-06</v>
       </c>
       <c r="J4" s="1">
-        <v>2.9720018473796935e-05</v>
+        <v>2.9721587546158016e-05</v>
       </c>
       <c r="K4" s="1">
-        <v>1.7465336139081125e-06</v>
+        <v>1.7436233705573354e-06</v>
       </c>
       <c r="L4" s="1">
-        <v>8.0510100453434308e-07</v>
+        <v>8.0864025425230813e-07</v>
       </c>
       <c r="M4" s="1">
-        <v>4.1362937172155907e-06</v>
+        <v>4.1411004574811057e-06</v>
       </c>
       <c r="N4" s="1">
-        <v>5.3671866179970612e-06</v>
+        <v>5.3771056355113376e-06</v>
       </c>
       <c r="O4" s="1">
-        <v>4.1136690577223709e-06</v>
+        <v>4.1450493705895344e-06</v>
       </c>
       <c r="P4" s="1">
-        <v>6.5381125154565845e-06</v>
+        <v>6.5410341791015424e-06</v>
       </c>
       <c r="Q4" s="1">
-        <v>-1.5867009729961549e-06</v>
+        <v>-1.5856734244843276e-06</v>
       </c>
       <c r="R4" s="1">
-        <v>3.4773920960139626e-07</v>
+        <v>3.4803396425762577e-07</v>
       </c>
       <c r="S4" s="1">
-        <v>5.7621354584622402e-08</v>
+        <v>5.8419823715117475e-08</v>
       </c>
       <c r="T4" s="1">
-        <v>-1.6660138192837104e-06</v>
+        <v>-1.663874448044276e-06</v>
       </c>
       <c r="U4" s="1">
-        <v>3.5742978713975272e-07</v>
+        <v>3.5779069650554093e-07</v>
       </c>
       <c r="V4" s="1">
-        <v>-2.0796683454570941e-06</v>
+        <v>-2.0808112647426741e-06</v>
       </c>
       <c r="W4" s="1">
-        <v>0.0014804186028314487</v>
+        <v>0.0014803431788469809</v>
       </c>
     </row>
     <row r="5">
@@ -799,70 +799,70 @@
         <v>31</v>
       </c>
       <c r="B5" s="1">
-        <v>0.48079326646395798</v>
+        <v>0.48085224644855545</v>
       </c>
       <c r="C5" s="1">
-        <v>-0.0043432813474923266</v>
+        <v>-0.0043438490856059645</v>
       </c>
       <c r="D5" s="1">
-        <v>-0.0017290735104626938</v>
+        <v>-0.0017293520164615309</v>
       </c>
       <c r="E5" s="1">
-        <v>1.3579336350247199e-05</v>
+        <v>1.3581998461224909e-05</v>
       </c>
       <c r="F5" s="1">
-        <v>0.013493828446089802</v>
+        <v>0.013495732533811236</v>
       </c>
       <c r="G5" s="1">
-        <v>0.004485850865684194</v>
+        <v>0.0044863802162231001</v>
       </c>
       <c r="H5" s="1">
-        <v>0.00074674967284705553</v>
+        <v>0.00075266352304363855</v>
       </c>
       <c r="I5" s="1">
-        <v>0.00095403239629371014</v>
+        <v>0.00095736360175242667</v>
       </c>
       <c r="J5" s="1">
-        <v>-0.00089496367754761386</v>
+        <v>-0.00089520163268240471</v>
       </c>
       <c r="K5" s="1">
-        <v>-0.0005150207332088215</v>
+        <v>-0.00051497695453430956</v>
       </c>
       <c r="L5" s="1">
-        <v>0.00033255059778972921</v>
+        <v>0.00033350892576967375</v>
       </c>
       <c r="M5" s="1">
-        <v>0.00078750142037764732</v>
+        <v>0.00078805359216170805</v>
       </c>
       <c r="N5" s="1">
-        <v>0.0008560558877677123</v>
+        <v>0.00085687023424588053</v>
       </c>
       <c r="O5" s="1">
-        <v>0.0012788983865768344</v>
+        <v>0.0012812418466102678</v>
       </c>
       <c r="P5" s="1">
-        <v>0.00050824674592876012</v>
+        <v>0.00050802708791718339</v>
       </c>
       <c r="Q5" s="1">
-        <v>0.00070061108926836209</v>
+        <v>0.00070107987534062319</v>
       </c>
       <c r="R5" s="1">
-        <v>0.00021720913303140306</v>
+        <v>0.00021739053027827575</v>
       </c>
       <c r="S5" s="1">
-        <v>-0.00033859932688944799</v>
+        <v>-0.000337184187624337</v>
       </c>
       <c r="T5" s="1">
-        <v>-0.00064835230723333647</v>
+        <v>-0.00064809810855500326</v>
       </c>
       <c r="U5" s="1">
-        <v>-4.7140348208480915e-05</v>
+        <v>-4.715701320879076e-05</v>
       </c>
       <c r="V5" s="1">
-        <v>-0.00033801629198465521</v>
+        <v>-0.00033817222213717787</v>
       </c>
       <c r="W5" s="1">
-        <v>0.055397169638454091</v>
+        <v>0.05539892111724587</v>
       </c>
     </row>
     <row r="6">
@@ -870,70 +870,70 @@
         <v>32</v>
       </c>
       <c r="B6" s="1">
-        <v>0.49388687406005005</v>
+        <v>0.49387029620098566</v>
       </c>
       <c r="C6" s="1">
-        <v>-0.0035172900119950475</v>
+        <v>-0.0035177170903658763</v>
       </c>
       <c r="D6" s="1">
-        <v>-0.0025644436865721043</v>
+        <v>-0.0025646656809372448</v>
       </c>
       <c r="E6" s="1">
-        <v>1.9346492382057382e-05</v>
+        <v>1.9348624443621138e-05</v>
       </c>
       <c r="F6" s="1">
-        <v>0.004485850865684194</v>
+        <v>0.0044863802162231001</v>
       </c>
       <c r="G6" s="1">
-        <v>0.013325509532998801</v>
+        <v>0.01332585024602672</v>
       </c>
       <c r="H6" s="1">
-        <v>0.00036800583366158532</v>
+        <v>0.00037606046244136569</v>
       </c>
       <c r="I6" s="1">
-        <v>0.00045972340606168297</v>
+        <v>0.00046736914627379042</v>
       </c>
       <c r="J6" s="1">
-        <v>0.0015712259760549754</v>
+        <v>0.0015714349319430748</v>
       </c>
       <c r="K6" s="1">
-        <v>-0.00036480244647054717</v>
+        <v>-0.00036514171179066225</v>
       </c>
       <c r="L6" s="1">
-        <v>0.00025244413595181155</v>
+        <v>0.00025329874919793102</v>
       </c>
       <c r="M6" s="1">
-        <v>0.00074021294388039276</v>
+        <v>0.00074136071649849502</v>
       </c>
       <c r="N6" s="1">
-        <v>0.00080256444823905045</v>
+        <v>0.00080426892555403653</v>
       </c>
       <c r="O6" s="1">
-        <v>0.00058234815539603621</v>
+        <v>0.00058658656497566613</v>
       </c>
       <c r="P6" s="1">
-        <v>0.00051332791660694925</v>
+        <v>0.00051378370076846959</v>
       </c>
       <c r="Q6" s="1">
-        <v>3.0248734445546127e-05</v>
+        <v>3.0393940106556924e-05</v>
       </c>
       <c r="R6" s="1">
-        <v>-0.00039942899568943049</v>
+        <v>-0.0003994328647871255</v>
       </c>
       <c r="S6" s="1">
-        <v>-0.00010856958028136569</v>
+        <v>-0.00010823442896788077</v>
       </c>
       <c r="T6" s="1">
-        <v>-0.0002946688086779255</v>
+        <v>-0.00029464157959173311</v>
       </c>
       <c r="U6" s="1">
-        <v>-3.8941505359787239e-05</v>
+        <v>-3.8889796764058227e-05</v>
       </c>
       <c r="V6" s="1">
-        <v>-0.00040147129838803697</v>
+        <v>-0.0004015178967798072</v>
       </c>
       <c r="W6" s="1">
-        <v>0.083340611684416421</v>
+        <v>0.083336933860581386</v>
       </c>
     </row>
     <row r="7">
@@ -941,70 +941,70 @@
         <v>33</v>
       </c>
       <c r="B7" s="1">
-        <v>0.017894070906440979</v>
+        <v>0.017107646062817058</v>
       </c>
       <c r="C7" s="1">
-        <v>-0.00045403456467682144</v>
+        <v>-0.00045489746242027872</v>
       </c>
       <c r="D7" s="1">
-        <v>-0.00036875802923581197</v>
+        <v>-0.00037785414271208906</v>
       </c>
       <c r="E7" s="1">
-        <v>3.0551793969262053e-06</v>
+        <v>3.1222932744982617e-06</v>
       </c>
       <c r="F7" s="1">
-        <v>0.00074674967284705553</v>
+        <v>0.00075266352304363855</v>
       </c>
       <c r="G7" s="1">
-        <v>0.00036800583366158532</v>
+        <v>0.00037606046244136569</v>
       </c>
       <c r="H7" s="1">
-        <v>0.0070475416825397045</v>
+        <v>0.0070537313786434748</v>
       </c>
       <c r="I7" s="1">
-        <v>0.0066037720101523806</v>
+        <v>0.0066102736986056974</v>
       </c>
       <c r="J7" s="1">
-        <v>0.00034226106314820222</v>
+        <v>0.00035699467006882455</v>
       </c>
       <c r="K7" s="1">
-        <v>0.00036841182855208108</v>
+        <v>0.00036704193284014679</v>
       </c>
       <c r="L7" s="1">
-        <v>0.00018331426375307278</v>
+        <v>0.00018580760837791081</v>
       </c>
       <c r="M7" s="1">
-        <v>0.00093475281900316082</v>
+        <v>0.00093853002727808975</v>
       </c>
       <c r="N7" s="1">
-        <v>0.0016036964443329475</v>
+        <v>0.0016080833383988</v>
       </c>
       <c r="O7" s="1">
-        <v>0.0041427608821523118</v>
+        <v>0.0041417654789060237</v>
       </c>
       <c r="P7" s="1">
-        <v>0.00012227405409102196</v>
+        <v>0.00012616687918747715</v>
       </c>
       <c r="Q7" s="1">
-        <v>0.00014122577129529757</v>
+        <v>0.00013873103132005507</v>
       </c>
       <c r="R7" s="1">
-        <v>6.4169881594070113e-05</v>
+        <v>6.2795084423893424e-05</v>
       </c>
       <c r="S7" s="1">
-        <v>3.6463763483209481e-05</v>
+        <v>3.6110355277742994e-05</v>
       </c>
       <c r="T7" s="1">
-        <v>-0.00010363729209104459</v>
+        <v>-0.00010785120479856077</v>
       </c>
       <c r="U7" s="1">
-        <v>8.264270228446951e-05</v>
+        <v>8.2224232057556267e-05</v>
       </c>
       <c r="V7" s="1">
-        <v>-0.00044624980382536008</v>
+        <v>-0.00044083872194012827</v>
       </c>
       <c r="W7" s="1">
-        <v>0.0023442321949717375</v>
+        <v>0.0026350454678028806</v>
       </c>
     </row>
     <row r="8">
@@ -1012,70 +1012,70 @@
         <v>34</v>
       </c>
       <c r="B8" s="1">
-        <v>-0.20005054095562219</v>
+        <v>-0.2008606090507673</v>
       </c>
       <c r="C8" s="1">
-        <v>-0.00062862017784685365</v>
+        <v>-0.00062948148366442349</v>
       </c>
       <c r="D8" s="1">
-        <v>0.00019750613892446922</v>
+        <v>0.00018875802709519135</v>
       </c>
       <c r="E8" s="1">
-        <v>-1.6752916890906602e-06</v>
+        <v>-1.6103820858560437e-06</v>
       </c>
       <c r="F8" s="1">
-        <v>0.00095403239629371014</v>
+        <v>0.00095736360175242667</v>
       </c>
       <c r="G8" s="1">
-        <v>0.00045972340606168297</v>
+        <v>0.00046736914627379042</v>
       </c>
       <c r="H8" s="1">
-        <v>0.0066037720101523806</v>
+        <v>0.0066102736986056974</v>
       </c>
       <c r="I8" s="1">
-        <v>0.0098547884483961463</v>
+        <v>0.0098611516092802255</v>
       </c>
       <c r="J8" s="1">
-        <v>3.7707549351796363e-05</v>
+        <v>5.2474444297274589e-05</v>
       </c>
       <c r="K8" s="1">
-        <v>-0.00010411751455254676</v>
+        <v>-0.00010574830557309365</v>
       </c>
       <c r="L8" s="1">
-        <v>-0.00011422653152577645</v>
+        <v>-0.0001113226203436912</v>
       </c>
       <c r="M8" s="1">
-        <v>0.0010128105142009852</v>
+        <v>0.0010173457892590494</v>
       </c>
       <c r="N8" s="1">
-        <v>0.0018782048088149517</v>
+        <v>0.0018831387773014284</v>
       </c>
       <c r="O8" s="1">
-        <v>0.0046503539211968396</v>
+        <v>0.0046502962896633315</v>
       </c>
       <c r="P8" s="1">
-        <v>0.00016912685371123616</v>
+        <v>0.00017367573120304503</v>
       </c>
       <c r="Q8" s="1">
-        <v>-8.083814694195314e-05</v>
+        <v>-8.356095843780947e-05</v>
       </c>
       <c r="R8" s="1">
-        <v>-0.00031906175583449855</v>
+        <v>-0.00032033638275109932</v>
       </c>
       <c r="S8" s="1">
-        <v>-0.00056885517052950247</v>
+        <v>-0.0005701000669414728</v>
       </c>
       <c r="T8" s="1">
-        <v>-0.00069645547336109133</v>
+        <v>-0.00070051481869081193</v>
       </c>
       <c r="U8" s="1">
-        <v>0.00012454348774739972</v>
+        <v>0.00012422120797319605</v>
       </c>
       <c r="V8" s="1">
-        <v>-0.00040660245896358485</v>
+        <v>-0.00040124313242675437</v>
       </c>
       <c r="W8" s="1">
-        <v>-0.014829157271021631</v>
+        <v>-0.014553455990840042</v>
       </c>
     </row>
     <row r="9">
@@ -1083,70 +1083,70 @@
         <v>35</v>
       </c>
       <c r="B9" s="1">
-        <v>1.1412065116883283</v>
+        <v>1.1411653623095526</v>
       </c>
       <c r="C9" s="1">
-        <v>0.0024207726028084727</v>
+        <v>0.0024201257037271876</v>
       </c>
       <c r="D9" s="1">
-        <v>-0.0042197139235300718</v>
+        <v>-0.0042198587556691453</v>
       </c>
       <c r="E9" s="1">
-        <v>2.9720018473796935e-05</v>
+        <v>2.9721587546158016e-05</v>
       </c>
       <c r="F9" s="1">
-        <v>-0.00089496367754761386</v>
+        <v>-0.00089520163268240471</v>
       </c>
       <c r="G9" s="1">
-        <v>0.0015712259760549754</v>
+        <v>0.0015714349319430748</v>
       </c>
       <c r="H9" s="1">
-        <v>0.00034226106314820222</v>
+        <v>0.00035699467006882455</v>
       </c>
       <c r="I9" s="1">
-        <v>3.7707549351796363e-05</v>
+        <v>5.2474444297274589e-05</v>
       </c>
       <c r="J9" s="1">
-        <v>0.0099691895969448441</v>
+        <v>0.0099696544326073125</v>
       </c>
       <c r="K9" s="1">
-        <v>-0.00069065715585138986</v>
+        <v>-0.0006913951854915952</v>
       </c>
       <c r="L9" s="1">
-        <v>0.00021780035553151025</v>
+        <v>0.00021648248353120948</v>
       </c>
       <c r="M9" s="1">
-        <v>0.00012018079190549832</v>
+        <v>0.00012036658941416093</v>
       </c>
       <c r="N9" s="1">
-        <v>1.367455279248711e-05</v>
+        <v>1.4996247580098543e-05</v>
       </c>
       <c r="O9" s="1">
-        <v>-0.00091702550134693979</v>
+        <v>-0.00091066254925988022</v>
       </c>
       <c r="P9" s="1">
-        <v>0.00093479597114506235</v>
+        <v>0.00093548547582276639</v>
       </c>
       <c r="Q9" s="1">
-        <v>-0.00056857325658396518</v>
+        <v>-0.00056866509352243924</v>
       </c>
       <c r="R9" s="1">
-        <v>0.00051202314542196994</v>
+        <v>0.00051195080170554283</v>
       </c>
       <c r="S9" s="1">
-        <v>0.00018286558056222757</v>
+        <v>0.00018272712905641544</v>
       </c>
       <c r="T9" s="1">
-        <v>3.3101782606645078e-05</v>
+        <v>3.3324099228680334e-05</v>
       </c>
       <c r="U9" s="1">
-        <v>-9.9683058348488951e-05</v>
+        <v>-9.9575054676820547e-05</v>
       </c>
       <c r="V9" s="1">
-        <v>0.00067257479913849366</v>
+        <v>0.00067231246177649334</v>
       </c>
       <c r="W9" s="1">
-        <v>0.14047956722483934</v>
+        <v>0.14046724417943945</v>
       </c>
     </row>
     <row r="10">
@@ -1154,70 +1154,70 @@
         <v>36</v>
       </c>
       <c r="B10" s="1">
-        <v>0.005571078924883799</v>
+        <v>0.0056383950453154528</v>
       </c>
       <c r="C10" s="1">
-        <v>0.00029269195668616169</v>
+        <v>0.00029283490894639478</v>
       </c>
       <c r="D10" s="1">
-        <v>-0.00024242926528108763</v>
+        <v>-0.00024203093231952091</v>
       </c>
       <c r="E10" s="1">
-        <v>1.7465336139081125e-06</v>
+        <v>1.7436233705573354e-06</v>
       </c>
       <c r="F10" s="1">
-        <v>-0.0005150207332088215</v>
+        <v>-0.00051497695453430956</v>
       </c>
       <c r="G10" s="1">
-        <v>-0.00036480244647054717</v>
+        <v>-0.00036514171179066225</v>
       </c>
       <c r="H10" s="1">
-        <v>0.00036841182855208108</v>
+        <v>0.00036704193284014679</v>
       </c>
       <c r="I10" s="1">
-        <v>-0.00010411751455254676</v>
+        <v>-0.00010574830557309365</v>
       </c>
       <c r="J10" s="1">
-        <v>-0.00069065715585138986</v>
+        <v>-0.0006913951854915952</v>
       </c>
       <c r="K10" s="1">
-        <v>0.0102440141489015</v>
+        <v>0.01024373025671103</v>
       </c>
       <c r="L10" s="1">
-        <v>0.00040977687561216246</v>
+        <v>0.00040974714625913731</v>
       </c>
       <c r="M10" s="1">
-        <v>0.0048932259311993071</v>
+        <v>0.004892617111327496</v>
       </c>
       <c r="N10" s="1">
-        <v>0.0083664059459030646</v>
+        <v>0.0083654625488858731</v>
       </c>
       <c r="O10" s="1">
-        <v>0.0093485706505276826</v>
+        <v>0.0093475011703379948</v>
       </c>
       <c r="P10" s="1">
-        <v>-0.001932533003049772</v>
+        <v>-0.0019327979388430079</v>
       </c>
       <c r="Q10" s="1">
-        <v>0.0004897618595911305</v>
+        <v>0.00048985668712317877</v>
       </c>
       <c r="R10" s="1">
-        <v>-0.00034761775020915168</v>
+        <v>-0.00034752641390990886</v>
       </c>
       <c r="S10" s="1">
-        <v>9.895330886552315e-05</v>
+        <v>9.9525197844504932e-05</v>
       </c>
       <c r="T10" s="1">
-        <v>0.00074195131851820066</v>
+        <v>0.00074203739800882758</v>
       </c>
       <c r="U10" s="1">
-        <v>7.9824604839555705e-05</v>
+        <v>7.9799327961025172e-05</v>
       </c>
       <c r="V10" s="1">
-        <v>0.00031537664029805809</v>
+        <v>0.00031549542225519246</v>
       </c>
       <c r="W10" s="1">
-        <v>-0.0026242751310778245</v>
+        <v>-0.0026351156412308674</v>
       </c>
     </row>
     <row r="11">
@@ -1225,70 +1225,70 @@
         <v>37</v>
       </c>
       <c r="B11" s="1">
-        <v>0.013573636299462339</v>
+        <v>0.013684389828636023</v>
       </c>
       <c r="C11" s="1">
-        <v>-0.00012708938582782503</v>
+        <v>-0.00012965564297623769</v>
       </c>
       <c r="D11" s="1">
-        <v>-0.00010698817308102404</v>
+        <v>-0.00010745327257397769</v>
       </c>
       <c r="E11" s="1">
-        <v>8.0510100453434308e-07</v>
+        <v>8.0864025425230813e-07</v>
       </c>
       <c r="F11" s="1">
-        <v>0.00033255059778972921</v>
+        <v>0.00033350892576967375</v>
       </c>
       <c r="G11" s="1">
-        <v>0.00025244413595181155</v>
+        <v>0.00025329874919793102</v>
       </c>
       <c r="H11" s="1">
-        <v>0.00018331426375307278</v>
+        <v>0.00018580760837791081</v>
       </c>
       <c r="I11" s="1">
-        <v>-0.00011422653152577645</v>
+        <v>-0.0001113226203436912</v>
       </c>
       <c r="J11" s="1">
-        <v>0.00021780035553151025</v>
+        <v>0.00021648248353120948</v>
       </c>
       <c r="K11" s="1">
-        <v>0.00040977687561216246</v>
+        <v>0.00040974714625913731</v>
       </c>
       <c r="L11" s="1">
-        <v>0.0043169758524108657</v>
+        <v>0.0043170290934732422</v>
       </c>
       <c r="M11" s="1">
-        <v>0.0022451816871453608</v>
+        <v>0.002245156709557986</v>
       </c>
       <c r="N11" s="1">
-        <v>0.0023556881619271244</v>
+        <v>0.0023556180596090159</v>
       </c>
       <c r="O11" s="1">
-        <v>0.0023876606409945025</v>
+        <v>0.0023888372852591154</v>
       </c>
       <c r="P11" s="1">
-        <v>-0.00016518691542564707</v>
+        <v>-0.00016322765215295976</v>
       </c>
       <c r="Q11" s="1">
-        <v>4.7317915806717808e-05</v>
+        <v>4.7319897162765152e-05</v>
       </c>
       <c r="R11" s="1">
-        <v>0.00023734691965852369</v>
+        <v>0.00023706334204335678</v>
       </c>
       <c r="S11" s="1">
-        <v>-5.7529837111975479e-05</v>
+        <v>-5.778984488047e-05</v>
       </c>
       <c r="T11" s="1">
-        <v>0.00028390863396146599</v>
+        <v>0.00028434960028266742</v>
       </c>
       <c r="U11" s="1">
-        <v>4.4566536832471807e-05</v>
+        <v>4.4972581177952066e-05</v>
       </c>
       <c r="V11" s="1">
-        <v>-0.00027817702265839112</v>
+        <v>-0.00027962740123586816</v>
       </c>
       <c r="W11" s="1">
-        <v>0.00015215908750021781</v>
+        <v>0.00016003383766634988</v>
       </c>
     </row>
     <row r="12">
@@ -1296,70 +1296,70 @@
         <v>38</v>
       </c>
       <c r="B12" s="1">
-        <v>0.2232241650489854</v>
+        <v>0.22322793990371509</v>
       </c>
       <c r="C12" s="1">
-        <v>-0.0010784240879178845</v>
+        <v>-0.0010800088675685963</v>
       </c>
       <c r="D12" s="1">
-        <v>-0.0004992319139945009</v>
+        <v>-0.00049987203046672479</v>
       </c>
       <c r="E12" s="1">
-        <v>4.1362937172155907e-06</v>
+        <v>4.1411004574811057e-06</v>
       </c>
       <c r="F12" s="1">
-        <v>0.00078750142037764732</v>
+        <v>0.00078805359216170805</v>
       </c>
       <c r="G12" s="1">
-        <v>0.00074021294388039276</v>
+        <v>0.00074136071649849502</v>
       </c>
       <c r="H12" s="1">
-        <v>0.00093475281900316082</v>
+        <v>0.00093853002727808975</v>
       </c>
       <c r="I12" s="1">
-        <v>0.0010128105142009852</v>
+        <v>0.0010173457892590494</v>
       </c>
       <c r="J12" s="1">
-        <v>0.00012018079190549832</v>
+        <v>0.00012036658941416093</v>
       </c>
       <c r="K12" s="1">
-        <v>0.0048932259311993071</v>
+        <v>0.004892617111327496</v>
       </c>
       <c r="L12" s="1">
-        <v>0.0022451816871453608</v>
+        <v>0.002245156709557986</v>
       </c>
       <c r="M12" s="1">
-        <v>0.0082866446847504518</v>
+        <v>0.0082867031897337334</v>
       </c>
       <c r="N12" s="1">
-        <v>0.0072229584251150098</v>
+        <v>0.0072230138221963721</v>
       </c>
       <c r="O12" s="1">
-        <v>0.0078416149237322905</v>
+        <v>0.0078428620463452826</v>
       </c>
       <c r="P12" s="1">
-        <v>0.00032349160485712589</v>
+        <v>0.00032485339865582661</v>
       </c>
       <c r="Q12" s="1">
-        <v>0.00023312019874504827</v>
+        <v>0.00023285346653627135</v>
       </c>
       <c r="R12" s="1">
-        <v>-0.00065833441010340469</v>
+        <v>-0.00065866982425367342</v>
       </c>
       <c r="S12" s="1">
-        <v>-0.00014839392842893955</v>
+        <v>-0.00014870893704831177</v>
       </c>
       <c r="T12" s="1">
-        <v>-0.00012973395920752844</v>
+        <v>-0.0001300081064772048</v>
       </c>
       <c r="U12" s="1">
-        <v>6.3333374999228079e-05</v>
+        <v>6.3558707612914692e-05</v>
       </c>
       <c r="V12" s="1">
-        <v>-0.00036019158130497306</v>
+        <v>-0.00036043366379014759</v>
       </c>
       <c r="W12" s="1">
-        <v>0.0062394237257273541</v>
+        <v>0.0062536191026427643</v>
       </c>
     </row>
     <row r="13">
@@ -1367,70 +1367,70 @@
         <v>39</v>
       </c>
       <c r="B13" s="1">
-        <v>0.079310626651220267</v>
+        <v>0.079269331535407814</v>
       </c>
       <c r="C13" s="1">
-        <v>-0.00066412106336970677</v>
+        <v>-0.00066559996694138266</v>
       </c>
       <c r="D13" s="1">
-        <v>-0.00062559994210271974</v>
+        <v>-0.00062692334473433975</v>
       </c>
       <c r="E13" s="1">
-        <v>5.3671866179970612e-06</v>
+        <v>5.3771056355113376e-06</v>
       </c>
       <c r="F13" s="1">
-        <v>0.0008560558877677123</v>
+        <v>0.00085687023424588053</v>
       </c>
       <c r="G13" s="1">
-        <v>0.00080256444823905045</v>
+        <v>0.00080426892555403653</v>
       </c>
       <c r="H13" s="1">
-        <v>0.0016036964443329475</v>
+        <v>0.0016080833383988</v>
       </c>
       <c r="I13" s="1">
-        <v>0.0018782048088149517</v>
+        <v>0.0018831387773014284</v>
       </c>
       <c r="J13" s="1">
-        <v>1.367455279248711e-05</v>
+        <v>1.4996247580098543e-05</v>
       </c>
       <c r="K13" s="1">
-        <v>0.0083664059459030646</v>
+        <v>0.0083654625488858731</v>
       </c>
       <c r="L13" s="1">
-        <v>0.0023556881619271244</v>
+        <v>0.0023556180596090159</v>
       </c>
       <c r="M13" s="1">
-        <v>0.0072229584251150098</v>
+        <v>0.0072230138221963721</v>
       </c>
       <c r="N13" s="1">
-        <v>0.013529717453636448</v>
+        <v>0.013529672249905226</v>
       </c>
       <c r="O13" s="1">
-        <v>0.011915063196623008</v>
+        <v>0.011915901935492697</v>
       </c>
       <c r="P13" s="1">
-        <v>0.00028183506807523992</v>
+        <v>0.00028340492913089127</v>
       </c>
       <c r="Q13" s="1">
-        <v>0.0004829639570982302</v>
+        <v>0.00048247573836460926</v>
       </c>
       <c r="R13" s="1">
-        <v>-0.00060930075877384943</v>
+        <v>-0.00060964309599903402</v>
       </c>
       <c r="S13" s="1">
-        <v>7.0604887186006019e-05</v>
+        <v>7.0456830842946733e-05</v>
       </c>
       <c r="T13" s="1">
-        <v>0.00033070095583536785</v>
+        <v>0.00033015168998388686</v>
       </c>
       <c r="U13" s="1">
-        <v>-1.6784392720941427e-05</v>
+        <v>-1.661774378293175e-05</v>
       </c>
       <c r="V13" s="1">
-        <v>0.00014079925065757981</v>
+        <v>0.00014116727141168933</v>
       </c>
       <c r="W13" s="1">
-        <v>0.0058141930016507026</v>
+        <v>0.005850489959625893</v>
       </c>
     </row>
     <row r="14">
@@ -1438,70 +1438,70 @@
         <v>40</v>
       </c>
       <c r="B14" s="1">
-        <v>-0.077048284017508184</v>
+        <v>-0.077340239137143954</v>
       </c>
       <c r="C14" s="1">
-        <v>-0.0014591975159760932</v>
+        <v>-0.001460569101181516</v>
       </c>
       <c r="D14" s="1">
-        <v>-0.0004470597490751349</v>
+        <v>-0.00045134032412479791</v>
       </c>
       <c r="E14" s="1">
-        <v>4.1136690577223709e-06</v>
+        <v>4.1450493705895344e-06</v>
       </c>
       <c r="F14" s="1">
-        <v>0.0012788983865768344</v>
+        <v>0.0012812418466102678</v>
       </c>
       <c r="G14" s="1">
-        <v>0.00058234815539603621</v>
+        <v>0.00058658656497566613</v>
       </c>
       <c r="H14" s="1">
-        <v>0.0041427608821523118</v>
+        <v>0.0041417654789060237</v>
       </c>
       <c r="I14" s="1">
-        <v>0.0046503539211968396</v>
+        <v>0.0046502962896633315</v>
       </c>
       <c r="J14" s="1">
-        <v>-0.00091702550134693979</v>
+        <v>-0.00091066254925988022</v>
       </c>
       <c r="K14" s="1">
-        <v>0.0093485706505276826</v>
+        <v>0.0093475011703379948</v>
       </c>
       <c r="L14" s="1">
-        <v>0.0023876606409945025</v>
+        <v>0.0023888372852591154</v>
       </c>
       <c r="M14" s="1">
-        <v>0.0078416149237322905</v>
+        <v>0.0078428620463452826</v>
       </c>
       <c r="N14" s="1">
-        <v>0.011915063196623008</v>
+        <v>0.011915901935492697</v>
       </c>
       <c r="O14" s="1">
-        <v>0.018608455216151995</v>
+        <v>0.018606115521158127</v>
       </c>
       <c r="P14" s="1">
-        <v>0.00019766908427390115</v>
+        <v>0.00020052188517340132</v>
       </c>
       <c r="Q14" s="1">
-        <v>0.00027248948223414292</v>
+        <v>0.00027113102312485737</v>
       </c>
       <c r="R14" s="1">
-        <v>-0.00075691862871956543</v>
+        <v>-0.00075786240772924912</v>
       </c>
       <c r="S14" s="1">
-        <v>-0.00010468013545307845</v>
+        <v>-0.00010519823288690044</v>
       </c>
       <c r="T14" s="1">
-        <v>0.0002453388474917486</v>
+        <v>0.00024297606506969204</v>
       </c>
       <c r="U14" s="1">
-        <v>7.6517614911248696e-05</v>
+        <v>7.6463604430427641e-05</v>
       </c>
       <c r="V14" s="1">
-        <v>-0.00022795056602183637</v>
+        <v>-0.00022531205847621007</v>
       </c>
       <c r="W14" s="1">
-        <v>-0.0042765602480863141</v>
+        <v>-0.0041366341835851889</v>
       </c>
     </row>
     <row r="15">
@@ -1509,70 +1509,70 @@
         <v>41</v>
       </c>
       <c r="B15" s="1">
-        <v>0.12061271939214008</v>
+        <v>0.12056767053899367</v>
       </c>
       <c r="C15" s="1">
-        <v>-0.00088671027620200959</v>
+        <v>-0.00088696305807333287</v>
       </c>
       <c r="D15" s="1">
-        <v>-0.00081617103811412045</v>
+        <v>-0.00081655362378963564</v>
       </c>
       <c r="E15" s="1">
-        <v>6.5381125154565845e-06</v>
+        <v>6.5410341791015424e-06</v>
       </c>
       <c r="F15" s="1">
-        <v>0.00050824674592876012</v>
+        <v>0.00050802708791718339</v>
       </c>
       <c r="G15" s="1">
-        <v>0.00051332791660694925</v>
+        <v>0.00051378370076846959</v>
       </c>
       <c r="H15" s="1">
-        <v>0.00012227405409102196</v>
+        <v>0.00012616687918747715</v>
       </c>
       <c r="I15" s="1">
-        <v>0.00016912685371123616</v>
+        <v>0.00017367573120304503</v>
       </c>
       <c r="J15" s="1">
-        <v>0.00093479597114506235</v>
+        <v>0.00093548547582276639</v>
       </c>
       <c r="K15" s="1">
-        <v>-0.001932533003049772</v>
+        <v>-0.0019327979388430079</v>
       </c>
       <c r="L15" s="1">
-        <v>-0.00016518691542564707</v>
+        <v>-0.00016322765215295976</v>
       </c>
       <c r="M15" s="1">
-        <v>0.00032349160485712589</v>
+        <v>0.00032485339865582661</v>
       </c>
       <c r="N15" s="1">
-        <v>0.00028183506807523992</v>
+        <v>0.00028340492913089127</v>
       </c>
       <c r="O15" s="1">
-        <v>0.00019766908427390115</v>
+        <v>0.00020052188517340132</v>
       </c>
       <c r="P15" s="1">
-        <v>0.0048574243706315245</v>
+        <v>0.0048574830258557343</v>
       </c>
       <c r="Q15" s="1">
-        <v>2.9808550461043158e-06</v>
+        <v>3.0135168577992422e-06</v>
       </c>
       <c r="R15" s="1">
-        <v>-5.9596746496676624e-05</v>
+        <v>-5.9591859712589427e-05</v>
       </c>
       <c r="S15" s="1">
-        <v>-8.9452140593747429e-05</v>
+        <v>-8.9709914237745721e-05</v>
       </c>
       <c r="T15" s="1">
-        <v>-0.00041460741557638645</v>
+        <v>-0.00041470842895323964</v>
       </c>
       <c r="U15" s="1">
-        <v>-2.7989357611484336e-05</v>
+        <v>-2.7919713257970103e-05</v>
       </c>
       <c r="V15" s="1">
-        <v>-0.0003388951088311061</v>
+        <v>-0.00033893738896588737</v>
       </c>
       <c r="W15" s="1">
-        <v>0.025638998954825409</v>
+        <v>0.025645010923495304</v>
       </c>
     </row>
     <row r="16">
@@ -1580,70 +1580,70 @@
         <v>42</v>
       </c>
       <c r="B16" s="1">
-        <v>-0.028847287456580384</v>
+        <v>-0.028841299162262909</v>
       </c>
       <c r="C16" s="1">
-        <v>-0.00031995136502455698</v>
+        <v>-0.00032002508144550251</v>
       </c>
       <c r="D16" s="1">
-        <v>0.00022777525906596957</v>
+        <v>0.00022762542451128243</v>
       </c>
       <c r="E16" s="1">
-        <v>-1.5867009729961549e-06</v>
+        <v>-1.5856734244843276e-06</v>
       </c>
       <c r="F16" s="1">
-        <v>0.00070061108926836209</v>
+        <v>0.00070107987534062319</v>
       </c>
       <c r="G16" s="1">
-        <v>3.0248734445546127e-05</v>
+        <v>3.0393940106556924e-05</v>
       </c>
       <c r="H16" s="1">
-        <v>0.00014122577129529757</v>
+        <v>0.00013873103132005507</v>
       </c>
       <c r="I16" s="1">
-        <v>-8.083814694195314e-05</v>
+        <v>-8.356095843780947e-05</v>
       </c>
       <c r="J16" s="1">
-        <v>-0.00056857325658396518</v>
+        <v>-0.00056866509352243924</v>
       </c>
       <c r="K16" s="1">
-        <v>0.0004897618595911305</v>
+        <v>0.00048985668712317877</v>
       </c>
       <c r="L16" s="1">
-        <v>4.7317915806717808e-05</v>
+        <v>4.7319897162765152e-05</v>
       </c>
       <c r="M16" s="1">
-        <v>0.00023312019874504827</v>
+        <v>0.00023285346653627135</v>
       </c>
       <c r="N16" s="1">
-        <v>0.0004829639570982302</v>
+        <v>0.00048247573836460926</v>
       </c>
       <c r="O16" s="1">
-        <v>0.00027248948223414292</v>
+        <v>0.00027113102312485737</v>
       </c>
       <c r="P16" s="1">
-        <v>2.9808550461043158e-06</v>
+        <v>3.0135168577992422e-06</v>
       </c>
       <c r="Q16" s="1">
-        <v>0.0062198170453504724</v>
+        <v>0.006219872241532887</v>
       </c>
       <c r="R16" s="1">
-        <v>0.0030506682191097307</v>
+        <v>0.0030506061102342484</v>
       </c>
       <c r="S16" s="1">
-        <v>0.0030421544291140169</v>
+        <v>0.0030421802534685953</v>
       </c>
       <c r="T16" s="1">
-        <v>0.0030826661094129626</v>
+        <v>0.0030825537512761186</v>
       </c>
       <c r="U16" s="1">
-        <v>7.9392012225257497e-05</v>
+        <v>7.9342928284943204e-05</v>
       </c>
       <c r="V16" s="1">
-        <v>-0.00076350103609910871</v>
+        <v>-0.00076330712344999411</v>
       </c>
       <c r="W16" s="1">
-        <v>-0.012019235986143254</v>
+        <v>-0.012010619107599915</v>
       </c>
     </row>
     <row r="17">
@@ -1651,70 +1651,70 @@
         <v>43</v>
       </c>
       <c r="B17" s="1">
-        <v>0.077336276651423827</v>
+        <v>0.077335506604728557</v>
       </c>
       <c r="C17" s="1">
-        <v>0.00020488079719342038</v>
+        <v>0.00020491099749257464</v>
       </c>
       <c r="D17" s="1">
-        <v>-6.2686421124072411e-05</v>
+        <v>-6.2739331759362194e-05</v>
       </c>
       <c r="E17" s="1">
-        <v>3.4773920960139626e-07</v>
+        <v>3.4803396425762577e-07</v>
       </c>
       <c r="F17" s="1">
-        <v>0.00021720913303140306</v>
+        <v>0.00021739053027827575</v>
       </c>
       <c r="G17" s="1">
-        <v>-0.00039942899568943049</v>
+        <v>-0.0003994328647871255</v>
       </c>
       <c r="H17" s="1">
-        <v>6.4169881594070113e-05</v>
+        <v>6.2795084423893424e-05</v>
       </c>
       <c r="I17" s="1">
-        <v>-0.00031906175583449855</v>
+        <v>-0.00032033638275109932</v>
       </c>
       <c r="J17" s="1">
-        <v>0.00051202314542196994</v>
+        <v>0.00051195080170554283</v>
       </c>
       <c r="K17" s="1">
-        <v>-0.00034761775020915168</v>
+        <v>-0.00034752641390990886</v>
       </c>
       <c r="L17" s="1">
-        <v>0.00023734691965852369</v>
+        <v>0.00023706334204335678</v>
       </c>
       <c r="M17" s="1">
-        <v>-0.00065833441010340469</v>
+        <v>-0.00065866982425367342</v>
       </c>
       <c r="N17" s="1">
-        <v>-0.00060930075877384943</v>
+        <v>-0.00060964309599903402</v>
       </c>
       <c r="O17" s="1">
-        <v>-0.00075691862871956543</v>
+        <v>-0.00075786240772924912</v>
       </c>
       <c r="P17" s="1">
-        <v>-5.9596746496676624e-05</v>
+        <v>-5.9591859712589427e-05</v>
       </c>
       <c r="Q17" s="1">
-        <v>0.0030506682191097307</v>
+        <v>0.0030506061102342484</v>
       </c>
       <c r="R17" s="1">
-        <v>0.0080926835948855157</v>
+        <v>0.0080924881681627824</v>
       </c>
       <c r="S17" s="1">
-        <v>0.0030949695727172048</v>
+        <v>0.0030949553698559435</v>
       </c>
       <c r="T17" s="1">
-        <v>0.0031361482906489108</v>
+        <v>0.0031361147030941074</v>
       </c>
       <c r="U17" s="1">
-        <v>3.6317115186274918e-05</v>
+        <v>3.6310583426534524e-05</v>
       </c>
       <c r="V17" s="1">
-        <v>-0.00068786024902307147</v>
+        <v>-0.00068778864189887731</v>
       </c>
       <c r="W17" s="1">
-        <v>-0.00060027503194808041</v>
+        <v>-0.00059653890084393479</v>
       </c>
     </row>
     <row r="18">
@@ -1722,70 +1722,70 @@
         <v>44</v>
       </c>
       <c r="B18" s="1">
-        <v>0.069537503792999708</v>
+        <v>0.069552456486487974</v>
       </c>
       <c r="C18" s="1">
-        <v>0.00011891873370873589</v>
+        <v>0.00011878012526927322</v>
       </c>
       <c r="D18" s="1">
-        <v>-1.1250208357280189e-05</v>
+        <v>-1.136353169683274e-05</v>
       </c>
       <c r="E18" s="1">
-        <v>5.7621354584622402e-08</v>
+        <v>5.8419823715117475e-08</v>
       </c>
       <c r="F18" s="1">
-        <v>-0.00033859932688944799</v>
+        <v>-0.000337184187624337</v>
       </c>
       <c r="G18" s="1">
-        <v>-0.00010856958028136569</v>
+        <v>-0.00010823442896788077</v>
       </c>
       <c r="H18" s="1">
-        <v>3.6463763483209481e-05</v>
+        <v>3.6110355277742994e-05</v>
       </c>
       <c r="I18" s="1">
-        <v>-0.00056885517052950247</v>
+        <v>-0.0005701000669414728</v>
       </c>
       <c r="J18" s="1">
-        <v>0.00018286558056222757</v>
+        <v>0.00018272712905641544</v>
       </c>
       <c r="K18" s="1">
-        <v>9.895330886552315e-05</v>
+        <v>9.9525197844504932e-05</v>
       </c>
       <c r="L18" s="1">
-        <v>-5.7529837111975479e-05</v>
+        <v>-5.778984488047e-05</v>
       </c>
       <c r="M18" s="1">
-        <v>-0.00014839392842893955</v>
+        <v>-0.00014870893704831177</v>
       </c>
       <c r="N18" s="1">
-        <v>7.0604887186006019e-05</v>
+        <v>7.0456830842946733e-05</v>
       </c>
       <c r="O18" s="1">
-        <v>-0.00010468013545307845</v>
+        <v>-0.00010519823288690044</v>
       </c>
       <c r="P18" s="1">
-        <v>-8.9452140593747429e-05</v>
+        <v>-8.9709914237745721e-05</v>
       </c>
       <c r="Q18" s="1">
-        <v>0.0030421544291140169</v>
+        <v>0.0030421802534685953</v>
       </c>
       <c r="R18" s="1">
-        <v>0.0030949695727172048</v>
+        <v>0.0030949553698559435</v>
       </c>
       <c r="S18" s="1">
-        <v>0.0063695223797432272</v>
+        <v>0.0063697064249529037</v>
       </c>
       <c r="T18" s="1">
-        <v>0.0031248954021580282</v>
+        <v>0.0031248929059409028</v>
       </c>
       <c r="U18" s="1">
-        <v>1.7737208756797327e-05</v>
+        <v>1.7670242752886191e-05</v>
       </c>
       <c r="V18" s="1">
-        <v>-0.00037665368842834505</v>
+        <v>-0.00037653561876798899</v>
       </c>
       <c r="W18" s="1">
-        <v>-0.0026690474041293905</v>
+        <v>-0.0026635480057327424</v>
       </c>
     </row>
     <row r="19">
@@ -1793,70 +1793,70 @@
         <v>45</v>
       </c>
       <c r="B19" s="1">
-        <v>0.1303673128721613</v>
+        <v>0.1303299574170482</v>
       </c>
       <c r="C19" s="1">
-        <v>0.00010815508494538728</v>
+        <v>0.00010850047922327704</v>
       </c>
       <c r="D19" s="1">
-        <v>0.00023156269370499041</v>
+        <v>0.00023124277766027948</v>
       </c>
       <c r="E19" s="1">
-        <v>-1.6660138192837104e-06</v>
+        <v>-1.663874448044276e-06</v>
       </c>
       <c r="F19" s="1">
-        <v>-0.00064835230723333647</v>
+        <v>-0.00064809810855500326</v>
       </c>
       <c r="G19" s="1">
-        <v>-0.0002946688086779255</v>
+        <v>-0.00029464157959173311</v>
       </c>
       <c r="H19" s="1">
-        <v>-0.00010363729209104459</v>
+        <v>-0.00010785120479856077</v>
       </c>
       <c r="I19" s="1">
-        <v>-0.00069645547336109133</v>
+        <v>-0.00070051481869081193</v>
       </c>
       <c r="J19" s="1">
-        <v>3.3101782606645078e-05</v>
+        <v>3.3324099228680334e-05</v>
       </c>
       <c r="K19" s="1">
-        <v>0.00074195131851820066</v>
+        <v>0.00074203739800882758</v>
       </c>
       <c r="L19" s="1">
-        <v>0.00028390863396146599</v>
+        <v>0.00028434960028266742</v>
       </c>
       <c r="M19" s="1">
-        <v>-0.00012973395920752844</v>
+        <v>-0.0001300081064772048</v>
       </c>
       <c r="N19" s="1">
-        <v>0.00033070095583536785</v>
+        <v>0.00033015168998388686</v>
       </c>
       <c r="O19" s="1">
-        <v>0.0002453388474917486</v>
+        <v>0.00024297606506969204</v>
       </c>
       <c r="P19" s="1">
-        <v>-0.00041460741557638645</v>
+        <v>-0.00041470842895323964</v>
       </c>
       <c r="Q19" s="1">
-        <v>0.0030826661094129626</v>
+        <v>0.0030825537512761186</v>
       </c>
       <c r="R19" s="1">
-        <v>0.0031361482906489108</v>
+        <v>0.0031361147030941074</v>
       </c>
       <c r="S19" s="1">
-        <v>0.0031248954021580282</v>
+        <v>0.0031248929059409028</v>
       </c>
       <c r="T19" s="1">
-        <v>0.0046890602962465231</v>
+        <v>0.0046889138405683747</v>
       </c>
       <c r="U19" s="1">
-        <v>4.9775669577739991e-07</v>
+        <v>4.6429249506987295e-07</v>
       </c>
       <c r="V19" s="1">
-        <v>-0.00026439729650003176</v>
+        <v>-0.00026426368470051638</v>
       </c>
       <c r="W19" s="1">
-        <v>-0.011154883995328491</v>
+        <v>-0.011139055401932177</v>
       </c>
     </row>
     <row r="20">
@@ -1864,70 +1864,70 @@
         <v>46</v>
       </c>
       <c r="B20" s="1">
-        <v>-0.037557332645023304</v>
+        <v>-0.037561996128989972</v>
       </c>
       <c r="C20" s="1">
-        <v>-5.9471605398852103e-05</v>
+        <v>-5.9472437166146412e-05</v>
       </c>
       <c r="D20" s="1">
-        <v>-4.5586323035425036e-05</v>
+        <v>-4.5637073072948148e-05</v>
       </c>
       <c r="E20" s="1">
-        <v>3.5742978713975272e-07</v>
+        <v>3.5779069650554093e-07</v>
       </c>
       <c r="F20" s="1">
-        <v>-4.7140348208480915e-05</v>
+        <v>-4.715701320879076e-05</v>
       </c>
       <c r="G20" s="1">
-        <v>-3.8941505359787239e-05</v>
+        <v>-3.8889796764058227e-05</v>
       </c>
       <c r="H20" s="1">
-        <v>8.264270228446951e-05</v>
+        <v>8.2224232057556267e-05</v>
       </c>
       <c r="I20" s="1">
-        <v>0.00012454348774739972</v>
+        <v>0.00012422120797319605</v>
       </c>
       <c r="J20" s="1">
-        <v>-9.9683058348488951e-05</v>
+        <v>-9.9575054676820547e-05</v>
       </c>
       <c r="K20" s="1">
-        <v>7.9824604839555705e-05</v>
+        <v>7.9799327961025172e-05</v>
       </c>
       <c r="L20" s="1">
-        <v>4.4566536832471807e-05</v>
+        <v>4.4972581177952066e-05</v>
       </c>
       <c r="M20" s="1">
-        <v>6.3333374999228079e-05</v>
+        <v>6.3558707612914692e-05</v>
       </c>
       <c r="N20" s="1">
-        <v>-1.6784392720941427e-05</v>
+        <v>-1.661774378293175e-05</v>
       </c>
       <c r="O20" s="1">
-        <v>7.6517614911248696e-05</v>
+        <v>7.6463604430427641e-05</v>
       </c>
       <c r="P20" s="1">
-        <v>-2.7989357611484336e-05</v>
+        <v>-2.7919713257970103e-05</v>
       </c>
       <c r="Q20" s="1">
-        <v>7.9392012225257497e-05</v>
+        <v>7.9342928284943204e-05</v>
       </c>
       <c r="R20" s="1">
-        <v>3.6317115186274918e-05</v>
+        <v>3.6310583426534524e-05</v>
       </c>
       <c r="S20" s="1">
-        <v>1.7737208756797327e-05</v>
+        <v>1.7670242752886191e-05</v>
       </c>
       <c r="T20" s="1">
-        <v>4.9775669577739991e-07</v>
+        <v>4.6429249506987295e-07</v>
       </c>
       <c r="U20" s="1">
-        <v>0.00012857416099429803</v>
+        <v>0.00012857105888305193</v>
       </c>
       <c r="V20" s="1">
-        <v>-0.00080098123070798839</v>
+        <v>-0.00080090098799894417</v>
       </c>
       <c r="W20" s="1">
-        <v>-0.00035665499525848465</v>
+        <v>-0.00035477966467830496</v>
       </c>
     </row>
     <row r="21">
@@ -1935,70 +1935,70 @@
         <v>47</v>
       </c>
       <c r="B21" s="1">
-        <v>0.55685721702818491</v>
+        <v>0.55685319257133536</v>
       </c>
       <c r="C21" s="1">
-        <v>0.00067779885389898783</v>
+        <v>0.00067759831483548121</v>
       </c>
       <c r="D21" s="1">
-        <v>0.00027214616557069693</v>
+        <v>0.00027232946578940875</v>
       </c>
       <c r="E21" s="1">
-        <v>-2.0796683454570941e-06</v>
+        <v>-2.0808112647426741e-06</v>
       </c>
       <c r="F21" s="1">
-        <v>-0.00033801629198465521</v>
+        <v>-0.00033817222213717787</v>
       </c>
       <c r="G21" s="1">
-        <v>-0.00040147129838803697</v>
+        <v>-0.0004015178967798072</v>
       </c>
       <c r="H21" s="1">
-        <v>-0.00044624980382536008</v>
+        <v>-0.00044083872194012827</v>
       </c>
       <c r="I21" s="1">
-        <v>-0.00040660245896358485</v>
+        <v>-0.00040124313242675437</v>
       </c>
       <c r="J21" s="1">
-        <v>0.00067257479913849366</v>
+        <v>0.00067231246177649334</v>
       </c>
       <c r="K21" s="1">
-        <v>0.00031537664029805809</v>
+        <v>0.00031549542225519246</v>
       </c>
       <c r="L21" s="1">
-        <v>-0.00027817702265839112</v>
+        <v>-0.00027962740123586816</v>
       </c>
       <c r="M21" s="1">
-        <v>-0.00036019158130497306</v>
+        <v>-0.00036043366379014759</v>
       </c>
       <c r="N21" s="1">
-        <v>0.00014079925065757981</v>
+        <v>0.00014116727141168933</v>
       </c>
       <c r="O21" s="1">
-        <v>-0.00022795056602183637</v>
+        <v>-0.00022531205847621007</v>
       </c>
       <c r="P21" s="1">
-        <v>-0.0003388951088311061</v>
+        <v>-0.00033893738896588737</v>
       </c>
       <c r="Q21" s="1">
-        <v>-0.00076350103609910871</v>
+        <v>-0.00076330712344999411</v>
       </c>
       <c r="R21" s="1">
-        <v>-0.00068786024902307147</v>
+        <v>-0.00068778864189887731</v>
       </c>
       <c r="S21" s="1">
-        <v>-0.00037665368842834505</v>
+        <v>-0.00037653561876798899</v>
       </c>
       <c r="T21" s="1">
-        <v>-0.00026439729650003176</v>
+        <v>-0.00026426368470051638</v>
       </c>
       <c r="U21" s="1">
-        <v>-0.00080098123070798839</v>
+        <v>-0.00080090098799894417</v>
       </c>
       <c r="V21" s="1">
-        <v>0.0075732872391260555</v>
+        <v>0.0075725945051740417</v>
       </c>
       <c r="W21" s="1">
-        <v>0.00028310852535623487</v>
+        <v>0.00027061107658671313</v>
       </c>
     </row>
     <row r="22">
@@ -2006,70 +2006,70 @@
         <v>48</v>
       </c>
       <c r="B22" s="1">
-        <v>-2.9406335547798501</v>
+        <v>-2.9400279871726389</v>
       </c>
       <c r="C22" s="1">
-        <v>0.0092155366467176481</v>
+        <v>0.0092038696369052819</v>
       </c>
       <c r="D22" s="1">
-        <v>-0.19270693019356422</v>
+        <v>-0.19269498968705623</v>
       </c>
       <c r="E22" s="1">
-        <v>0.0014804186028314487</v>
+        <v>0.0014803431788469809</v>
       </c>
       <c r="F22" s="1">
-        <v>0.055397169638454091</v>
+        <v>0.05539892111724587</v>
       </c>
       <c r="G22" s="1">
-        <v>0.083340611684416421</v>
+        <v>0.083336933860581386</v>
       </c>
       <c r="H22" s="1">
-        <v>0.0023442321949717375</v>
+        <v>0.0026350454678028806</v>
       </c>
       <c r="I22" s="1">
-        <v>-0.014829157271021631</v>
+        <v>-0.014553455990840042</v>
       </c>
       <c r="J22" s="1">
-        <v>0.14047956722483934</v>
+        <v>0.14046724417943945</v>
       </c>
       <c r="K22" s="1">
-        <v>-0.0026242751310778245</v>
+        <v>-0.0026351156412308674</v>
       </c>
       <c r="L22" s="1">
-        <v>0.00015215908750021781</v>
+        <v>0.00016003383766634988</v>
       </c>
       <c r="M22" s="1">
-        <v>0.0062394237257273541</v>
+        <v>0.0062536191026427643</v>
       </c>
       <c r="N22" s="1">
-        <v>0.0058141930016507026</v>
+        <v>0.005850489959625893</v>
       </c>
       <c r="O22" s="1">
-        <v>-0.0042765602480863141</v>
+        <v>-0.0041366341835851889</v>
       </c>
       <c r="P22" s="1">
-        <v>0.025638998954825409</v>
+        <v>0.025645010923495304</v>
       </c>
       <c r="Q22" s="1">
-        <v>-0.012019235986143254</v>
+        <v>-0.012010619107599915</v>
       </c>
       <c r="R22" s="1">
-        <v>-0.00060027503194808041</v>
+        <v>-0.00059653890084393479</v>
       </c>
       <c r="S22" s="1">
-        <v>-0.0026690474041293905</v>
+        <v>-0.0026635480057327424</v>
       </c>
       <c r="T22" s="1">
-        <v>-0.011154883995328491</v>
+        <v>-0.011139055401932177</v>
       </c>
       <c r="U22" s="1">
-        <v>-0.00035665499525848465</v>
+        <v>-0.00035477966467830496</v>
       </c>
       <c r="V22" s="1">
-        <v>0.00028310852535623487</v>
+        <v>0.00027061107658671313</v>
       </c>
       <c r="W22" s="1">
-        <v>6.1035764466240607</v>
+        <v>6.1028328603437103</v>
       </c>
     </row>
   </sheetData>
@@ -2178,91 +2178,91 @@
         <v>28</v>
       </c>
       <c r="B2" s="1">
-        <v>0.111179614980015</v>
+        <v>0.11122728304557684</v>
       </c>
       <c r="C2" s="1">
-        <v>0.0021218729957004417</v>
+        <v>0.0021216969169983442</v>
       </c>
       <c r="D2" s="1">
-        <v>-0.00061111466669012417</v>
+        <v>-0.00061139435826157722</v>
       </c>
       <c r="E2" s="1">
-        <v>4.0633669123015998e-06</v>
+        <v>4.0659937396979263e-06</v>
       </c>
       <c r="F2" s="1">
-        <v>-0.001002733217395422</v>
+        <v>-0.0010028728390685453</v>
       </c>
       <c r="G2" s="1">
-        <v>-0.00071658188276470204</v>
+        <v>-0.00071678963033238461</v>
       </c>
       <c r="H2" s="1">
-        <v>9.1360855844900665e-05</v>
+        <v>9.2002540408303926e-05</v>
       </c>
       <c r="I2" s="1">
-        <v>0.00013220040657819284</v>
+        <v>0.00013274493500439781</v>
       </c>
       <c r="J2" s="1">
-        <v>0.0013388933282844351</v>
+        <v>0.0013385692587229345</v>
       </c>
       <c r="K2" s="1">
-        <v>0.00091215519520853184</v>
+        <v>0.00091136835275431552</v>
       </c>
       <c r="L2" s="1">
-        <v>-0.00032688432689244762</v>
+        <v>-0.00032654109911471087</v>
       </c>
       <c r="M2" s="1">
-        <v>-1.3651675430555719e-05</v>
+        <v>-2.0070048017606238e-05</v>
       </c>
       <c r="N2" s="1">
-        <v>2.9813092838635712e-05</v>
+        <v>2.6261133151250088e-05</v>
       </c>
       <c r="O2" s="1">
-        <v>0.00010932454707247114</v>
+        <v>0.00010574717743388378</v>
       </c>
       <c r="P2" s="1">
-        <v>6.3650887609722432e-06</v>
+        <v>2.8786150530319375e-06</v>
       </c>
       <c r="Q2" s="1">
-        <v>-0.00069754342896915069</v>
+        <v>-0.00069705987500229532</v>
       </c>
       <c r="R2" s="1">
-        <v>8.4262788811329068e-05</v>
+        <v>8.4081874091737748e-05</v>
       </c>
       <c r="S2" s="1">
-        <v>0.00064089701780007768</v>
+        <v>0.00064111944641499329</v>
       </c>
       <c r="T2" s="1">
-        <v>0.0006114966993194319</v>
+        <v>0.00061150156097970819</v>
       </c>
       <c r="U2" s="1">
-        <v>1.3775632837375327e-05</v>
+        <v>1.3756852253357047e-05</v>
       </c>
       <c r="V2" s="1">
-        <v>3.6419482317014877e-05</v>
+        <v>3.6395070718797619e-05</v>
       </c>
       <c r="W2" s="1">
-        <v>-0.00031636551779414294</v>
+        <v>-0.00031625325709478758</v>
       </c>
       <c r="X2" s="1">
-        <v>-0.00014499133940875926</v>
+        <v>-0.00014466675143836758</v>
       </c>
       <c r="Y2" s="1">
-        <v>-0.0002349981681333789</v>
+        <v>-0.0002347743718051137</v>
       </c>
       <c r="Z2" s="1">
-        <v>-0.00014321333190522639</v>
+        <v>-0.0001431394394607211</v>
       </c>
       <c r="AA2" s="1">
-        <v>3.0703270238637221e-05</v>
+        <v>3.0697361751528114e-05</v>
       </c>
       <c r="AB2" s="1">
-        <v>-0.00014938282282643371</v>
+        <v>-0.00014931307563693409</v>
       </c>
       <c r="AC2" s="1">
-        <v>0.0002211027817161787</v>
+        <v>0.00022126216367576983</v>
       </c>
       <c r="AD2" s="1">
-        <v>0.019711053348858452</v>
+        <v>0.019721756836726327</v>
       </c>
     </row>
     <row r="3">
@@ -2270,91 +2270,91 @@
         <v>29</v>
       </c>
       <c r="B3" s="1">
-        <v>0.30835987205720189</v>
+        <v>0.3084120638030437</v>
       </c>
       <c r="C3" s="1">
-        <v>-0.00061111466669012417</v>
+        <v>-0.00061139435826157722</v>
       </c>
       <c r="D3" s="1">
-        <v>0.0043431742413440307</v>
+        <v>0.0043422963488050463</v>
       </c>
       <c r="E3" s="1">
-        <v>-3.5089711007528992e-05</v>
+        <v>-3.5081414680118658e-05</v>
       </c>
       <c r="F3" s="1">
-        <v>-0.00063012782969449135</v>
+        <v>-0.00063055682422203524</v>
       </c>
       <c r="G3" s="1">
-        <v>-0.00074509641453213149</v>
+        <v>-0.00074566902273696251</v>
       </c>
       <c r="H3" s="1">
-        <v>-4.3576820902117147e-05</v>
+        <v>-4.3252319829737047e-05</v>
       </c>
       <c r="I3" s="1">
-        <v>0.00019214737901620865</v>
+        <v>0.00019249919574610926</v>
       </c>
       <c r="J3" s="1">
-        <v>-0.0011566271942825084</v>
+        <v>-0.0011576299035292417</v>
       </c>
       <c r="K3" s="1">
-        <v>-0.0012907005816245268</v>
+        <v>-0.0012912037879911301</v>
       </c>
       <c r="L3" s="1">
-        <v>0.0010485905521277949</v>
+        <v>0.0010492415154944902</v>
       </c>
       <c r="M3" s="1">
-        <v>-4.6420195275274391e-05</v>
+        <v>-4.2572220413234808e-05</v>
       </c>
       <c r="N3" s="1">
-        <v>-0.00012014014089925529</v>
+        <v>-0.0001183365358152326</v>
       </c>
       <c r="O3" s="1">
-        <v>-0.00058124179032388243</v>
+        <v>-0.00057924310768332418</v>
       </c>
       <c r="P3" s="1">
-        <v>-0.00040893668337514157</v>
+        <v>-0.00040697468991459165</v>
       </c>
       <c r="Q3" s="1">
-        <v>0.00023924200194067741</v>
+        <v>0.00024036456956684146</v>
       </c>
       <c r="R3" s="1">
-        <v>0.0003912964687543645</v>
+        <v>0.0003903885445184184</v>
       </c>
       <c r="S3" s="1">
-        <v>-0.00082936790661555272</v>
+        <v>-0.00082849223526633084</v>
       </c>
       <c r="T3" s="1">
-        <v>-0.00081423433782255774</v>
+        <v>-0.00081414227336978028</v>
       </c>
       <c r="U3" s="1">
-        <v>5.9748764067758808e-06</v>
+        <v>5.9998282366802158e-06</v>
       </c>
       <c r="V3" s="1">
-        <v>-0.00015052663880638431</v>
+        <v>-0.00014937979534815349</v>
       </c>
       <c r="W3" s="1">
-        <v>0.00027940960703747714</v>
+        <v>0.0002794308690572192</v>
       </c>
       <c r="X3" s="1">
-        <v>0.00013153047600365786</v>
+        <v>0.00013170998465468486</v>
       </c>
       <c r="Y3" s="1">
-        <v>0.00031990649440274271</v>
+        <v>0.00032016539832730589</v>
       </c>
       <c r="Z3" s="1">
-        <v>0.00032568306113439638</v>
+        <v>0.00032583794046796809</v>
       </c>
       <c r="AA3" s="1">
-        <v>-2.9222324530963489e-05</v>
+        <v>-2.9162967033968638e-05</v>
       </c>
       <c r="AB3" s="1">
-        <v>0.0002685045399632921</v>
+        <v>0.00026811463243268246</v>
       </c>
       <c r="AC3" s="1">
-        <v>0.00083672985607417816</v>
+        <v>0.00083610422314628341</v>
       </c>
       <c r="AD3" s="1">
-        <v>-0.13177490175099238</v>
+        <v>-0.13175468460728296</v>
       </c>
     </row>
     <row r="4">
@@ -2362,91 +2362,91 @@
         <v>30</v>
       </c>
       <c r="B4" s="1">
-        <v>-0.0023136740014522276</v>
+        <v>-0.0023141534668236936</v>
       </c>
       <c r="C4" s="1">
-        <v>4.0633669123015998e-06</v>
+        <v>4.0659937396979263e-06</v>
       </c>
       <c r="D4" s="1">
-        <v>-3.5089711007528992e-05</v>
+        <v>-3.5081414680118658e-05</v>
       </c>
       <c r="E4" s="1">
-        <v>2.8582022672068028e-07</v>
+        <v>2.8574245089209702e-07</v>
       </c>
       <c r="F4" s="1">
-        <v>5.392891861287464e-06</v>
+        <v>5.396088303639046e-06</v>
       </c>
       <c r="G4" s="1">
-        <v>6.0072571211060213e-06</v>
+        <v>6.012080848394124e-06</v>
       </c>
       <c r="H4" s="1">
-        <v>5.1252391178691032e-07</v>
+        <v>5.1090763831978842e-07</v>
       </c>
       <c r="I4" s="1">
-        <v>-1.645363971724841e-06</v>
+        <v>-1.6475174531387783e-06</v>
       </c>
       <c r="J4" s="1">
-        <v>7.6007713062086369e-06</v>
+        <v>7.6100248983638221e-06</v>
       </c>
       <c r="K4" s="1">
-        <v>9.9909765922426931e-06</v>
+        <v>9.995967118636885e-06</v>
       </c>
       <c r="L4" s="1">
-        <v>-8.1970071981256028e-06</v>
+        <v>-8.2031261962044221e-06</v>
       </c>
       <c r="M4" s="1">
-        <v>5.9977018582777852e-07</v>
+        <v>5.6922039002877799e-07</v>
       </c>
       <c r="N4" s="1">
-        <v>1.090203443377709e-06</v>
+        <v>1.0772143952623298e-06</v>
       </c>
       <c r="O4" s="1">
-        <v>4.9228315008932903e-06</v>
+        <v>4.908240151453141e-06</v>
       </c>
       <c r="P4" s="1">
-        <v>3.6696851312948998e-06</v>
+        <v>3.6556982154547368e-06</v>
       </c>
       <c r="Q4" s="1">
-        <v>-1.6842521293228784e-06</v>
+        <v>-1.6944316605496993e-06</v>
       </c>
       <c r="R4" s="1">
-        <v>-4.1542477240590948e-06</v>
+        <v>-4.146521257258857e-06</v>
       </c>
       <c r="S4" s="1">
-        <v>6.9433638656307321e-06</v>
+        <v>6.935389507512304e-06</v>
       </c>
       <c r="T4" s="1">
-        <v>6.7904105808029526e-06</v>
+        <v>6.7898444520005528e-06</v>
       </c>
       <c r="U4" s="1">
-        <v>-8.1450508840141085e-08</v>
+        <v>-8.1543469037379575e-08</v>
       </c>
       <c r="V4" s="1">
-        <v>1.339236452010717e-06</v>
+        <v>1.3300668113350449e-06</v>
       </c>
       <c r="W4" s="1">
-        <v>-1.955251280088958e-06</v>
+        <v>-1.9553974809714131e-06</v>
       </c>
       <c r="X4" s="1">
-        <v>-1.0118871289766911e-06</v>
+        <v>-1.013769504586189e-06</v>
       </c>
       <c r="Y4" s="1">
-        <v>-2.3239462200045692e-06</v>
+        <v>-2.3264625613003296e-06</v>
       </c>
       <c r="Z4" s="1">
-        <v>-2.4783066057005307e-06</v>
+        <v>-2.4794692075943287e-06</v>
       </c>
       <c r="AA4" s="1">
-        <v>2.2397388846689137e-07</v>
+        <v>2.2345195283460088e-07</v>
       </c>
       <c r="AB4" s="1">
-        <v>-2.0769142357174569e-06</v>
+        <v>-2.0740468800289598e-06</v>
       </c>
       <c r="AC4" s="1">
-        <v>-6.8888329484087388e-06</v>
+        <v>-6.8834032390387937e-06</v>
       </c>
       <c r="AD4" s="1">
-        <v>0.0010574311244198882</v>
+        <v>0.0010572319726645572</v>
       </c>
     </row>
     <row r="5">
@@ -2454,91 +2454,91 @@
         <v>31</v>
       </c>
       <c r="B5" s="1">
-        <v>0.32430556512071318</v>
+        <v>0.32430368511447116</v>
       </c>
       <c r="C5" s="1">
-        <v>-0.001002733217395422</v>
+        <v>-0.0010028728390685453</v>
       </c>
       <c r="D5" s="1">
-        <v>-0.00063012782969449135</v>
+        <v>-0.00063055682422203524</v>
       </c>
       <c r="E5" s="1">
-        <v>5.392891861287464e-06</v>
+        <v>5.396088303639046e-06</v>
       </c>
       <c r="F5" s="1">
-        <v>0.0032233203078495479</v>
+        <v>0.0032245462792804495</v>
       </c>
       <c r="G5" s="1">
-        <v>0.0011633448763302507</v>
+        <v>0.0011638356303170618</v>
       </c>
       <c r="H5" s="1">
-        <v>-0.00018359909847643773</v>
+        <v>-0.00018526002621138812</v>
       </c>
       <c r="I5" s="1">
-        <v>-0.00011339716233033407</v>
+        <v>-0.00011481690572052279</v>
       </c>
       <c r="J5" s="1">
-        <v>-0.00044024646550445187</v>
+        <v>-0.00044024364175349084</v>
       </c>
       <c r="K5" s="1">
-        <v>-0.0001199444807743269</v>
+        <v>-0.00011978665333909136</v>
       </c>
       <c r="L5" s="1">
-        <v>-0.00011608428662584071</v>
+        <v>-0.00011631613289262479</v>
       </c>
       <c r="M5" s="1">
-        <v>-0.0001430768577187695</v>
+        <v>-0.00014846996394472811</v>
       </c>
       <c r="N5" s="1">
-        <v>-0.00031990956719275907</v>
+        <v>-0.0003236951676087816</v>
       </c>
       <c r="O5" s="1">
-        <v>-0.00010034932850354686</v>
+        <v>-0.0001042105591575037</v>
       </c>
       <c r="P5" s="1">
-        <v>-0.00019862245929399549</v>
+        <v>-0.00020286750977572404</v>
       </c>
       <c r="Q5" s="1">
-        <v>4.2506254764311524e-05</v>
+        <v>4.2583379924906323e-05</v>
       </c>
       <c r="R5" s="1">
-        <v>-0.00040748308329207651</v>
+        <v>-0.00040709119719720913</v>
       </c>
       <c r="S5" s="1">
-        <v>0.00027582664246725676</v>
+        <v>0.00027594476830014938</v>
       </c>
       <c r="T5" s="1">
-        <v>0.00029943046820353741</v>
+        <v>0.0002990988169313878</v>
       </c>
       <c r="U5" s="1">
-        <v>-0.00012530015091925199</v>
+        <v>-0.00012545708909244765</v>
       </c>
       <c r="V5" s="1">
-        <v>-4.1666978713212136e-05</v>
+        <v>-4.2942995505832957e-05</v>
       </c>
       <c r="W5" s="1">
-        <v>0.00011242442893759884</v>
+        <v>0.00011233181646577196</v>
       </c>
       <c r="X5" s="1">
-        <v>8.0661687157407031e-05</v>
+        <v>8.037196471648864e-05</v>
       </c>
       <c r="Y5" s="1">
-        <v>-8.6648802190905649e-06</v>
+        <v>-8.8147579414155769e-06</v>
       </c>
       <c r="Z5" s="1">
-        <v>-0.00010666944760849778</v>
+        <v>-0.00010688810083355404</v>
       </c>
       <c r="AA5" s="1">
-        <v>-4.1469965185513902e-05</v>
+        <v>-4.1502926154004952e-05</v>
       </c>
       <c r="AB5" s="1">
-        <v>0.00010312410555349955</v>
+        <v>0.00010384759538335266</v>
       </c>
       <c r="AC5" s="1">
-        <v>-0.00060091668902185168</v>
+        <v>-0.00060060371219394088</v>
       </c>
       <c r="AD5" s="1">
-        <v>0.01979925068080483</v>
+        <v>0.019819251177696499</v>
       </c>
     </row>
     <row r="6">
@@ -2546,91 +2546,91 @@
         <v>32</v>
       </c>
       <c r="B6" s="1">
-        <v>0.44776656865424985</v>
+        <v>0.44781787384933142</v>
       </c>
       <c r="C6" s="1">
-        <v>-0.00071658188276470204</v>
+        <v>-0.00071678963033238461</v>
       </c>
       <c r="D6" s="1">
-        <v>-0.00074509641453213149</v>
+        <v>-0.00074566902273696251</v>
       </c>
       <c r="E6" s="1">
-        <v>6.0072571211060213e-06</v>
+        <v>6.012080848394124e-06</v>
       </c>
       <c r="F6" s="1">
-        <v>0.0011633448763302507</v>
+        <v>0.0011638356303170618</v>
       </c>
       <c r="G6" s="1">
-        <v>0.0035209230469872427</v>
+        <v>0.0035206408043594517</v>
       </c>
       <c r="H6" s="1">
-        <v>-0.00030796442428083722</v>
+        <v>-0.00031093000367299469</v>
       </c>
       <c r="I6" s="1">
-        <v>-0.00019165319355460419</v>
+        <v>-0.00019419607075122451</v>
       </c>
       <c r="J6" s="1">
-        <v>0.00015413176665688224</v>
+        <v>0.00015368537914614192</v>
       </c>
       <c r="K6" s="1">
-        <v>3.6110820475761772e-05</v>
+        <v>3.6302573137916242e-05</v>
       </c>
       <c r="L6" s="1">
-        <v>-7.836361564748996e-05</v>
+        <v>-7.8143548691798743e-05</v>
       </c>
       <c r="M6" s="1">
-        <v>-0.00011548397124611478</v>
+        <v>-0.00011187391820508138</v>
       </c>
       <c r="N6" s="1">
-        <v>-0.0003744352102762194</v>
+        <v>-0.00037281194019027006</v>
       </c>
       <c r="O6" s="1">
-        <v>-9.2882367042159981e-05</v>
+        <v>-9.1308260034307902e-05</v>
       </c>
       <c r="P6" s="1">
-        <v>-0.00015507968315515291</v>
+        <v>-0.00015421848968381587</v>
       </c>
       <c r="Q6" s="1">
-        <v>-4.2584902731655945e-05</v>
+        <v>-4.2248131494016135e-05</v>
       </c>
       <c r="R6" s="1">
-        <v>-0.00041320111576919737</v>
+        <v>-0.00041339875495975328</v>
       </c>
       <c r="S6" s="1">
-        <v>0.00024156228234947048</v>
+        <v>0.00024173667028505423</v>
       </c>
       <c r="T6" s="1">
-        <v>0.00022219611793040613</v>
+        <v>0.00022213145078145099</v>
       </c>
       <c r="U6" s="1">
-        <v>-0.00021874024278582729</v>
+        <v>-0.00021874189018649716</v>
       </c>
       <c r="V6" s="1">
-        <v>0.00018414739386359881</v>
+        <v>0.00018370270405850073</v>
       </c>
       <c r="W6" s="1">
-        <v>2.9470276791886477e-05</v>
+        <v>2.9563091247094761e-05</v>
       </c>
       <c r="X6" s="1">
-        <v>0.00015162865180272291</v>
+        <v>0.00015183067948679641</v>
       </c>
       <c r="Y6" s="1">
-        <v>-1.326514163258255e-06</v>
+        <v>-1.2081151540745821e-06</v>
       </c>
       <c r="Z6" s="1">
-        <v>-0.00026135917427633736</v>
+        <v>-0.00026140331547696172</v>
       </c>
       <c r="AA6" s="1">
-        <v>-2.3702041378156772e-05</v>
+        <v>-2.3704785514092833e-05</v>
       </c>
       <c r="AB6" s="1">
-        <v>6.7344656424772609e-05</v>
+        <v>6.7931593062165591e-05</v>
       </c>
       <c r="AC6" s="1">
-        <v>-0.00079515778733485823</v>
+        <v>-0.0007953618640864149</v>
       </c>
       <c r="AD6" s="1">
-        <v>0.023950738703727503</v>
+        <v>0.023968867584844549</v>
       </c>
     </row>
     <row r="7">
@@ -2638,91 +2638,91 @@
         <v>33</v>
       </c>
       <c r="B7" s="1">
-        <v>0.050707186686276905</v>
+        <v>0.049920406015456879</v>
       </c>
       <c r="C7" s="1">
-        <v>9.1360855844900665e-05</v>
+        <v>9.2002540408303926e-05</v>
       </c>
       <c r="D7" s="1">
-        <v>-4.3576820902117147e-05</v>
+        <v>-4.3252319829737047e-05</v>
       </c>
       <c r="E7" s="1">
-        <v>5.1252391178691032e-07</v>
+        <v>5.1090763831978842e-07</v>
       </c>
       <c r="F7" s="1">
-        <v>-0.00018359909847643773</v>
+        <v>-0.00018526002621138812</v>
       </c>
       <c r="G7" s="1">
-        <v>-0.00030796442428083722</v>
+        <v>-0.00031093000367299469</v>
       </c>
       <c r="H7" s="1">
-        <v>0.0024951466208067929</v>
+        <v>0.0024976351926219794</v>
       </c>
       <c r="I7" s="1">
-        <v>0.0022663906206026518</v>
+        <v>0.0022687175189009708</v>
       </c>
       <c r="J7" s="1">
-        <v>0.0002697225666177137</v>
+        <v>0.00027000401969211557</v>
       </c>
       <c r="K7" s="1">
-        <v>-2.4317605541686826e-05</v>
+        <v>-2.3814937422836336e-05</v>
       </c>
       <c r="L7" s="1">
-        <v>-0.00030646487566951124</v>
+        <v>-0.00030644486699942457</v>
       </c>
       <c r="M7" s="1">
-        <v>-5.1615494221616702e-06</v>
+        <v>5.276471611163135e-06</v>
       </c>
       <c r="N7" s="1">
-        <v>1.4544125403497823e-05</v>
+        <v>2.0763788420526163e-05</v>
       </c>
       <c r="O7" s="1">
-        <v>0.00022584273992496128</v>
+        <v>0.00023201929755199566</v>
       </c>
       <c r="P7" s="1">
-        <v>0.00075483529409155496</v>
+        <v>0.00076125599964115204</v>
       </c>
       <c r="Q7" s="1">
-        <v>-9.4509089046827311e-06</v>
+        <v>-9.6837172638545611e-06</v>
       </c>
       <c r="R7" s="1">
-        <v>0.00013469660076571624</v>
+        <v>0.00013407976979868354</v>
       </c>
       <c r="S7" s="1">
-        <v>-1.3740734714760779e-05</v>
+        <v>-1.39000627221119e-05</v>
       </c>
       <c r="T7" s="1">
-        <v>-7.8623942769521219e-05</v>
+        <v>-7.984045103867018e-05</v>
       </c>
       <c r="U7" s="1">
-        <v>8.7984862407354314e-05</v>
+        <v>8.8645211204724245e-05</v>
       </c>
       <c r="V7" s="1">
-        <v>3.4630650701491291e-05</v>
+        <v>3.5420483081301127e-05</v>
       </c>
       <c r="W7" s="1">
-        <v>9.2133671906330589e-05</v>
+        <v>9.424261472959993e-05</v>
       </c>
       <c r="X7" s="1">
-        <v>0.00017296126625769364</v>
+        <v>0.0001737357466902442</v>
       </c>
       <c r="Y7" s="1">
-        <v>0.00015930161468260249</v>
+        <v>0.00016151554315779585</v>
       </c>
       <c r="Z7" s="1">
-        <v>0.00022271922939599251</v>
+        <v>0.00022511645484702536</v>
       </c>
       <c r="AA7" s="1">
-        <v>1.1864831868659847e-05</v>
+        <v>1.2157059467935861e-05</v>
       </c>
       <c r="AB7" s="1">
-        <v>-7.5047214200771447e-05</v>
+        <v>-7.7427768856582163e-05</v>
       </c>
       <c r="AC7" s="1">
-        <v>0.00031453555330878086</v>
+        <v>0.00031371494295415994</v>
       </c>
       <c r="AD7" s="1">
-        <v>-0.0021186799020329471</v>
+        <v>-0.0021475786777238283</v>
       </c>
     </row>
     <row r="8">
@@ -2730,91 +2730,91 @@
         <v>34</v>
       </c>
       <c r="B8" s="1">
-        <v>-0.081909387821284152</v>
+        <v>-0.082698354033229574</v>
       </c>
       <c r="C8" s="1">
-        <v>0.00013220040657819284</v>
+        <v>0.00013274493500439781</v>
       </c>
       <c r="D8" s="1">
-        <v>0.00019214737901620865</v>
+        <v>0.00019249919574610926</v>
       </c>
       <c r="E8" s="1">
-        <v>-1.645363971724841e-06</v>
+        <v>-1.6475174531387783e-06</v>
       </c>
       <c r="F8" s="1">
-        <v>-0.00011339716233033407</v>
+        <v>-0.00011481690572052279</v>
       </c>
       <c r="G8" s="1">
-        <v>-0.00019165319355460419</v>
+        <v>-0.00019419607075122451</v>
       </c>
       <c r="H8" s="1">
-        <v>0.0022663906206026518</v>
+        <v>0.0022687175189009708</v>
       </c>
       <c r="I8" s="1">
-        <v>0.0041473967253799222</v>
+        <v>0.0041495257176200626</v>
       </c>
       <c r="J8" s="1">
-        <v>0.00043122981086106318</v>
+        <v>0.00043171746298547263</v>
       </c>
       <c r="K8" s="1">
-        <v>-3.8416975230696484e-05</v>
+        <v>-3.8214951402456719e-05</v>
       </c>
       <c r="L8" s="1">
-        <v>-0.00060606938195816625</v>
+        <v>-0.0006062907361732504</v>
       </c>
       <c r="M8" s="1">
-        <v>-2.3830766864432545e-06</v>
+        <v>-1.1261108089470628e-06</v>
       </c>
       <c r="N8" s="1">
-        <v>1.4613827423485214e-05</v>
+        <v>1.5744528860563026e-05</v>
       </c>
       <c r="O8" s="1">
-        <v>0.00037898017835450538</v>
+        <v>0.00037998077714232454</v>
       </c>
       <c r="P8" s="1">
-        <v>0.00099592322559639975</v>
+        <v>0.00099708613078575018</v>
       </c>
       <c r="Q8" s="1">
-        <v>0.00014269493493104655</v>
+        <v>0.00014240229746623391</v>
       </c>
       <c r="R8" s="1">
-        <v>0.0001166578478593224</v>
+        <v>0.00011627824684830692</v>
       </c>
       <c r="S8" s="1">
-        <v>-0.00012874124670425572</v>
+        <v>-0.00012859858556031891</v>
       </c>
       <c r="T8" s="1">
-        <v>2.7953952769162768e-06</v>
+        <v>1.5055522240919005e-06</v>
       </c>
       <c r="U8" s="1">
-        <v>1.6699583377934729e-05</v>
+        <v>1.716506834285739e-05</v>
       </c>
       <c r="V8" s="1">
-        <v>-2.4130707402652543e-05</v>
+        <v>-2.3698774530202076e-05</v>
       </c>
       <c r="W8" s="1">
-        <v>-5.2400507175013765e-05</v>
+        <v>-5.0397281129728206e-05</v>
       </c>
       <c r="X8" s="1">
-        <v>0.00011938926591684692</v>
+        <v>0.00012017143654060234</v>
       </c>
       <c r="Y8" s="1">
-        <v>3.630845010161492e-05</v>
+        <v>3.8517321355710987e-05</v>
       </c>
       <c r="Z8" s="1">
-        <v>4.7063208081767277e-06</v>
+        <v>6.7206320466746449e-06</v>
       </c>
       <c r="AA8" s="1">
-        <v>4.4045655337365065e-05</v>
+        <v>4.4273995539666791e-05</v>
       </c>
       <c r="AB8" s="1">
-        <v>-0.00016184415147045008</v>
+        <v>-0.00016383343116172216</v>
       </c>
       <c r="AC8" s="1">
-        <v>-3.5474930879192705e-05</v>
+        <v>-3.5852264965414039e-05</v>
       </c>
       <c r="AD8" s="1">
-        <v>-0.0090396172880511782</v>
+        <v>-0.009061612667918037</v>
       </c>
     </row>
     <row r="9">
@@ -2822,91 +2822,91 @@
         <v>35</v>
       </c>
       <c r="B9" s="1">
-        <v>1.3771243319650082</v>
+        <v>1.3770718425275383</v>
       </c>
       <c r="C9" s="1">
-        <v>0.0013388933282844351</v>
+        <v>0.0013385692587229345</v>
       </c>
       <c r="D9" s="1">
-        <v>-0.0011566271942825084</v>
+        <v>-0.0011576299035292417</v>
       </c>
       <c r="E9" s="1">
-        <v>7.6007713062086369e-06</v>
+        <v>7.6100248983638221e-06</v>
       </c>
       <c r="F9" s="1">
-        <v>-0.00044024646550445187</v>
+        <v>-0.00044024364175349084</v>
       </c>
       <c r="G9" s="1">
-        <v>0.00015413176665688224</v>
+        <v>0.00015368537914614192</v>
       </c>
       <c r="H9" s="1">
-        <v>0.0002697225666177137</v>
+        <v>0.00027000401969211557</v>
       </c>
       <c r="I9" s="1">
-        <v>0.00043122981086106318</v>
+        <v>0.00043171746298547263</v>
       </c>
       <c r="J9" s="1">
-        <v>0.0040825574873665643</v>
+        <v>0.0040814835928148748</v>
       </c>
       <c r="K9" s="1">
-        <v>0.0017213075233478913</v>
+        <v>0.0017201770546015874</v>
       </c>
       <c r="L9" s="1">
-        <v>-0.0024135051615365548</v>
+        <v>-0.0024126961360264902</v>
       </c>
       <c r="M9" s="1">
-        <v>-0.00021113830958135121</v>
+        <v>-0.00021249057078632759</v>
       </c>
       <c r="N9" s="1">
-        <v>-0.0003206725812040006</v>
+        <v>-0.00032269184100630377</v>
       </c>
       <c r="O9" s="1">
-        <v>0.00015165966043909713</v>
+        <v>0.00014965998320214571</v>
       </c>
       <c r="P9" s="1">
-        <v>-0.00021128741394695402</v>
+        <v>-0.00021334747518492788</v>
       </c>
       <c r="Q9" s="1">
-        <v>-0.00041794680650147258</v>
+        <v>-0.00041706959052231567</v>
       </c>
       <c r="R9" s="1">
-        <v>-0.00011973231116640753</v>
+        <v>-0.00012012337938340905</v>
       </c>
       <c r="S9" s="1">
-        <v>-0.00013056200243810774</v>
+        <v>-0.00012945392406336017</v>
       </c>
       <c r="T9" s="1">
-        <v>-0.00026544081782506747</v>
+        <v>-0.00026558822653842163</v>
       </c>
       <c r="U9" s="1">
-        <v>-0.00024503968109940768</v>
+        <v>-0.0002449540754716995</v>
       </c>
       <c r="V9" s="1">
-        <v>0.0002319188340691472</v>
+        <v>0.00023178251570455137</v>
       </c>
       <c r="W9" s="1">
-        <v>-0.00030843252272358222</v>
+        <v>-0.00030815426234148099</v>
       </c>
       <c r="X9" s="1">
-        <v>-9.3671063306771763e-05</v>
+        <v>-9.3192080305325078e-05</v>
       </c>
       <c r="Y9" s="1">
-        <v>-0.0002765266385888093</v>
+        <v>-0.00027580934530650167</v>
       </c>
       <c r="Z9" s="1">
-        <v>-0.0003537630662279605</v>
+        <v>-0.00035348041078906225</v>
       </c>
       <c r="AA9" s="1">
-        <v>3.789383106304176e-05</v>
+        <v>3.7976274810383837e-05</v>
       </c>
       <c r="AB9" s="1">
-        <v>-0.00039601807025534087</v>
+        <v>-0.00039614339558507528</v>
       </c>
       <c r="AC9" s="1">
-        <v>-0.00082130121834357909</v>
+        <v>-0.00082169616808810183</v>
       </c>
       <c r="AD9" s="1">
-        <v>0.039084426417537642</v>
+        <v>0.039111917202489729</v>
       </c>
     </row>
     <row r="10">
@@ -2914,91 +2914,91 @@
         <v>36</v>
       </c>
       <c r="B10" s="1">
-        <v>0.27332371717629278</v>
+        <v>0.27353728263249394</v>
       </c>
       <c r="C10" s="1">
-        <v>0.00091215519520853184</v>
+        <v>0.00091136835275431552</v>
       </c>
       <c r="D10" s="1">
-        <v>-0.0012907005816245268</v>
+        <v>-0.0012912037879911301</v>
       </c>
       <c r="E10" s="1">
-        <v>9.9909765922426931e-06</v>
+        <v>9.995967118636885e-06</v>
       </c>
       <c r="F10" s="1">
-        <v>-0.0001199444807743269</v>
+        <v>-0.00011978665333909136</v>
       </c>
       <c r="G10" s="1">
-        <v>3.6110820475761772e-05</v>
+        <v>3.6302573137916242e-05</v>
       </c>
       <c r="H10" s="1">
-        <v>-2.4317605541686826e-05</v>
+        <v>-2.3814937422836336e-05</v>
       </c>
       <c r="I10" s="1">
-        <v>-3.8416975230696484e-05</v>
+        <v>-3.8214951402456719e-05</v>
       </c>
       <c r="J10" s="1">
-        <v>0.0017213075233478913</v>
+        <v>0.0017201770546015874</v>
       </c>
       <c r="K10" s="1">
-        <v>0.0034115173668432209</v>
+        <v>0.0034103069061414736</v>
       </c>
       <c r="L10" s="1">
-        <v>-0.0020629642156984513</v>
+        <v>-0.0020621371954241698</v>
       </c>
       <c r="M10" s="1">
-        <v>-6.2923632151161773e-05</v>
+        <v>-5.7483896335475973e-05</v>
       </c>
       <c r="N10" s="1">
-        <v>0.00050869280587645567</v>
+        <v>0.00051062935803644475</v>
       </c>
       <c r="O10" s="1">
-        <v>0.0014688328919243879</v>
+        <v>0.0014708022138916952</v>
       </c>
       <c r="P10" s="1">
-        <v>0.0012372802067025339</v>
+        <v>0.0012393954563837324</v>
       </c>
       <c r="Q10" s="1">
-        <v>-0.0011882352697712467</v>
+        <v>-0.0011874621532563057</v>
       </c>
       <c r="R10" s="1">
-        <v>-7.4251394028742473e-05</v>
+        <v>-7.4548379598208083e-05</v>
       </c>
       <c r="S10" s="1">
-        <v>-1.734992209942687e-05</v>
+        <v>-1.7176389620661214e-05</v>
       </c>
       <c r="T10" s="1">
-        <v>8.1879965698179551e-05</v>
+        <v>8.1979349749285464e-05</v>
       </c>
       <c r="U10" s="1">
-        <v>-0.00013564933317826016</v>
+        <v>-0.00013550568942595245</v>
       </c>
       <c r="V10" s="1">
-        <v>0.00037540304085696398</v>
+        <v>0.00037548087850716109</v>
       </c>
       <c r="W10" s="1">
-        <v>-0.00025011880627297093</v>
+        <v>-0.00025000183947172902</v>
       </c>
       <c r="X10" s="1">
-        <v>-0.00017278947335544099</v>
+        <v>-0.00017246788388097448</v>
       </c>
       <c r="Y10" s="1">
-        <v>-0.0002913559535498415</v>
+        <v>-0.0002909556186508085</v>
       </c>
       <c r="Z10" s="1">
-        <v>-0.00020017749659223029</v>
+        <v>-0.00020003549311915485</v>
       </c>
       <c r="AA10" s="1">
-        <v>4.7795688513482006e-05</v>
+        <v>4.77923895057867e-05</v>
       </c>
       <c r="AB10" s="1">
-        <v>-0.00015274400946346009</v>
+        <v>-0.00015215913720350964</v>
       </c>
       <c r="AC10" s="1">
-        <v>-0.00070005291004656496</v>
+        <v>-0.00070035658455277941</v>
       </c>
       <c r="AD10" s="1">
-        <v>0.03800647758800986</v>
+        <v>0.038016998220714963</v>
       </c>
     </row>
     <row r="11">
@@ -3006,91 +3006,91 @@
         <v>50</v>
       </c>
       <c r="B11" s="1">
-        <v>0.031818378202738327</v>
+        <v>0.031939487038368922</v>
       </c>
       <c r="C11" s="1">
-        <v>-0.00032688432689244762</v>
+        <v>-0.00032654109911471087</v>
       </c>
       <c r="D11" s="1">
-        <v>0.0010485905521277949</v>
+        <v>0.0010492415154944902</v>
       </c>
       <c r="E11" s="1">
-        <v>-8.1970071981256028e-06</v>
+        <v>-8.2031261962044221e-06</v>
       </c>
       <c r="F11" s="1">
-        <v>-0.00011608428662584071</v>
+        <v>-0.00011631613289262479</v>
       </c>
       <c r="G11" s="1">
-        <v>-7.836361564748996e-05</v>
+        <v>-7.8143548691798743e-05</v>
       </c>
       <c r="H11" s="1">
-        <v>-0.00030646487566951124</v>
+        <v>-0.00030644486699942457</v>
       </c>
       <c r="I11" s="1">
-        <v>-0.00060606938195816625</v>
+        <v>-0.0006062907361732504</v>
       </c>
       <c r="J11" s="1">
-        <v>-0.0024135051615365548</v>
+        <v>-0.0024126961360264902</v>
       </c>
       <c r="K11" s="1">
-        <v>-0.0020629642156984513</v>
+        <v>-0.0020621371954241698</v>
       </c>
       <c r="L11" s="1">
-        <v>0.0044365660983415722</v>
+        <v>0.0044359981071651778</v>
       </c>
       <c r="M11" s="1">
-        <v>0.00016703052687095475</v>
+        <v>0.00016746398887032324</v>
       </c>
       <c r="N11" s="1">
-        <v>0.00074091303675060966</v>
+        <v>0.00074232998540966003</v>
       </c>
       <c r="O11" s="1">
-        <v>0.00011589681868736889</v>
+        <v>0.00011730365898865387</v>
       </c>
       <c r="P11" s="1">
-        <v>0.00048883646339116765</v>
+        <v>0.00049028559032506425</v>
       </c>
       <c r="Q11" s="1">
-        <v>6.8904080738087497e-06</v>
+        <v>6.1280332287918084e-06</v>
       </c>
       <c r="R11" s="1">
-        <v>0.00012300619782789159</v>
+        <v>0.00012331879840838468</v>
       </c>
       <c r="S11" s="1">
-        <v>8.9771476946931309e-05</v>
+        <v>8.8555117112579923e-05</v>
       </c>
       <c r="T11" s="1">
-        <v>-6.2234975630878414e-05</v>
+        <v>-6.2088709636105364e-05</v>
       </c>
       <c r="U11" s="1">
-        <v>0.0003638498635348257</v>
+        <v>0.0003636152840151588</v>
       </c>
       <c r="V11" s="1">
-        <v>-0.0003331633263491752</v>
+        <v>-0.00033280467288483804</v>
       </c>
       <c r="W11" s="1">
-        <v>0.00014704362225899744</v>
+        <v>0.00014685493987238074</v>
       </c>
       <c r="X11" s="1">
-        <v>1.7358690679364781e-05</v>
+        <v>1.7342659240487284e-05</v>
       </c>
       <c r="Y11" s="1">
-        <v>0.00010927461134957602</v>
+        <v>0.00010871025376677954</v>
       </c>
       <c r="Z11" s="1">
-        <v>0.00026314914437211876</v>
+        <v>0.00026304739543073501</v>
       </c>
       <c r="AA11" s="1">
-        <v>-3.2950987603140802e-05</v>
+        <v>-3.3009955384617144e-05</v>
       </c>
       <c r="AB11" s="1">
-        <v>0.00021068570771874207</v>
+        <v>0.00021062266988180849</v>
       </c>
       <c r="AC11" s="1">
-        <v>0.0007668974569817517</v>
+        <v>0.00076717438656892902</v>
       </c>
       <c r="AD11" s="1">
-        <v>-0.031952590189943696</v>
+        <v>-0.031970204997042347</v>
       </c>
     </row>
     <row r="12">
@@ -3098,91 +3098,91 @@
         <v>37</v>
       </c>
       <c r="B12" s="1">
-        <v>0.0056183050479927865</v>
+        <v>0.012112768768966739</v>
       </c>
       <c r="C12" s="1">
-        <v>-1.3651675430555719e-05</v>
+        <v>-2.0070048017606238e-05</v>
       </c>
       <c r="D12" s="1">
-        <v>-4.6420195275274391e-05</v>
+        <v>-4.2572220413234808e-05</v>
       </c>
       <c r="E12" s="1">
-        <v>5.9977018582777852e-07</v>
+        <v>5.6922039002877799e-07</v>
       </c>
       <c r="F12" s="1">
-        <v>-0.0001430768577187695</v>
+        <v>-0.00014846996394472811</v>
       </c>
       <c r="G12" s="1">
-        <v>-0.00011548397124611478</v>
+        <v>-0.00011187391820508138</v>
       </c>
       <c r="H12" s="1">
-        <v>-5.1615494221616702e-06</v>
+        <v>5.276471611163135e-06</v>
       </c>
       <c r="I12" s="1">
-        <v>-2.3830766864432545e-06</v>
+        <v>-1.1261108089470628e-06</v>
       </c>
       <c r="J12" s="1">
-        <v>-0.00021113830958135121</v>
+        <v>-0.00021249057078632759</v>
       </c>
       <c r="K12" s="1">
-        <v>-6.2923632151161773e-05</v>
+        <v>-5.7483896335475973e-05</v>
       </c>
       <c r="L12" s="1">
-        <v>0.00016703052687095475</v>
+        <v>0.00016746398887032324</v>
       </c>
       <c r="M12" s="1">
-        <v>0.0040242270545519047</v>
+        <v>0.0040281085966850988</v>
       </c>
       <c r="N12" s="1">
-        <v>0.002155726489486589</v>
+        <v>0.0021831390621273321</v>
       </c>
       <c r="O12" s="1">
-        <v>0.002196204698253055</v>
+        <v>0.0022252340016767204</v>
       </c>
       <c r="P12" s="1">
-        <v>0.0022013280760299053</v>
+        <v>0.0022336383737806354</v>
       </c>
       <c r="Q12" s="1">
-        <v>0.00020701937767074872</v>
+        <v>0.00020103124865936389</v>
       </c>
       <c r="R12" s="1">
-        <v>-0.00016997608527821563</v>
+        <v>-0.00016714156273139939</v>
       </c>
       <c r="S12" s="1">
-        <v>0.00012971782276768214</v>
+        <v>0.00010439556845814558</v>
       </c>
       <c r="T12" s="1">
-        <v>4.6936817608976696e-05</v>
+        <v>5.6099798986346735e-05</v>
       </c>
       <c r="U12" s="1">
-        <v>2.3557686489050344e-05</v>
+        <v>2.4484113650679814e-05</v>
       </c>
       <c r="V12" s="1">
-        <v>0.00033157118438130006</v>
+        <v>0.00034756903216696239</v>
       </c>
       <c r="W12" s="1">
-        <v>2.6077675107084495e-05</v>
+        <v>2.6669175055226498e-05</v>
       </c>
       <c r="X12" s="1">
-        <v>0.00010795880567861864</v>
+        <v>0.00011171655575287036</v>
       </c>
       <c r="Y12" s="1">
-        <v>8.0453958298756182e-05</v>
+        <v>7.6164394857071828e-05</v>
       </c>
       <c r="Z12" s="1">
-        <v>8.2996413472358744e-05</v>
+        <v>8.5366144347252679e-05</v>
       </c>
       <c r="AA12" s="1">
-        <v>2.3884410275531563e-05</v>
+        <v>2.2998047651115298e-05</v>
       </c>
       <c r="AB12" s="1">
-        <v>-0.00015704919902300352</v>
+        <v>-0.00015262677757495375</v>
       </c>
       <c r="AC12" s="1">
-        <v>-0.00023363686829847529</v>
+        <v>-0.00023501872157951839</v>
       </c>
       <c r="AD12" s="1">
-        <v>-0.001888738302854711</v>
+        <v>-0.0020290847390083333</v>
       </c>
     </row>
     <row r="13">
@@ -3190,91 +3190,91 @@
         <v>38</v>
       </c>
       <c r="B13" s="1">
-        <v>0.052837524752490886</v>
+        <v>0.056413441391103061</v>
       </c>
       <c r="C13" s="1">
-        <v>2.9813092838635712e-05</v>
+        <v>2.6261133151250088e-05</v>
       </c>
       <c r="D13" s="1">
-        <v>-0.00012014014089925529</v>
+        <v>-0.0001183365358152326</v>
       </c>
       <c r="E13" s="1">
-        <v>1.090203443377709e-06</v>
+        <v>1.0772143952623298e-06</v>
       </c>
       <c r="F13" s="1">
-        <v>-0.00031990956719275907</v>
+        <v>-0.0003236951676087816</v>
       </c>
       <c r="G13" s="1">
-        <v>-0.0003744352102762194</v>
+        <v>-0.00037281194019027006</v>
       </c>
       <c r="H13" s="1">
-        <v>1.4544125403497823e-05</v>
+        <v>2.0763788420526163e-05</v>
       </c>
       <c r="I13" s="1">
-        <v>1.4613827423485214e-05</v>
+        <v>1.5744528860563026e-05</v>
       </c>
       <c r="J13" s="1">
-        <v>-0.0003206725812040006</v>
+        <v>-0.00032269184100630377</v>
       </c>
       <c r="K13" s="1">
-        <v>0.00050869280587645567</v>
+        <v>0.00051062935803644475</v>
       </c>
       <c r="L13" s="1">
-        <v>0.00074091303675060966</v>
+        <v>0.00074232998540966003</v>
       </c>
       <c r="M13" s="1">
-        <v>0.002155726489486589</v>
+        <v>0.0021831390621273321</v>
       </c>
       <c r="N13" s="1">
-        <v>0.003861300243455849</v>
+        <v>0.0038891235142562526</v>
       </c>
       <c r="O13" s="1">
-        <v>0.0032329483638377167</v>
+        <v>0.0032616717111737534</v>
       </c>
       <c r="P13" s="1">
-        <v>0.003472752243249045</v>
+        <v>0.0035033137031109402</v>
       </c>
       <c r="Q13" s="1">
-        <v>0.00017006508000365033</v>
+        <v>0.00016782071755349584</v>
       </c>
       <c r="R13" s="1">
-        <v>8.7274665589687293e-05</v>
+        <v>8.7945962661358152e-05</v>
       </c>
       <c r="S13" s="1">
-        <v>-0.00014419974736451776</v>
+        <v>-0.00015715895350435134</v>
       </c>
       <c r="T13" s="1">
-        <v>-0.00017695988687609483</v>
+        <v>-0.00017134504534634093</v>
       </c>
       <c r="U13" s="1">
-        <v>0.00073173858196808289</v>
+        <v>0.00073213020111707297</v>
       </c>
       <c r="V13" s="1">
-        <v>-9.2917665589716133e-05</v>
+        <v>-8.2709880215469289e-05</v>
       </c>
       <c r="W13" s="1">
-        <v>-9.1689557595698505e-05</v>
+        <v>-9.1350099976601567e-05</v>
       </c>
       <c r="X13" s="1">
-        <v>-0.00021504076679775336</v>
+        <v>-0.00021260949092050623</v>
       </c>
       <c r="Y13" s="1">
-        <v>-0.00011389947680730429</v>
+        <v>-0.00011576996550806721</v>
       </c>
       <c r="Z13" s="1">
-        <v>0.00013911857936758836</v>
+        <v>0.00014074932097476645</v>
       </c>
       <c r="AA13" s="1">
-        <v>1.0801158396994855e-05</v>
+        <v>1.0429926402464023e-05</v>
       </c>
       <c r="AB13" s="1">
-        <v>-0.0001501203449077006</v>
+        <v>-0.00014831023249386424</v>
       </c>
       <c r="AC13" s="1">
-        <v>0.00024091415119737727</v>
+        <v>0.00023892831001505531</v>
       </c>
       <c r="AD13" s="1">
-        <v>-0.00048640755020138565</v>
+        <v>-0.00057305017629436829</v>
       </c>
     </row>
     <row r="14">
@@ -3282,91 +3282,91 @@
         <v>39</v>
       </c>
       <c r="B14" s="1">
-        <v>0.036844161690119913</v>
+        <v>0.040421349140300308</v>
       </c>
       <c r="C14" s="1">
-        <v>0.00010932454707247114</v>
+        <v>0.00010574717743388378</v>
       </c>
       <c r="D14" s="1">
-        <v>-0.00058124179032388243</v>
+        <v>-0.00057924310768332418</v>
       </c>
       <c r="E14" s="1">
-        <v>4.9228315008932903e-06</v>
+        <v>4.908240151453141e-06</v>
       </c>
       <c r="F14" s="1">
-        <v>-0.00010034932850354686</v>
+        <v>-0.0001042105591575037</v>
       </c>
       <c r="G14" s="1">
-        <v>-9.2882367042159981e-05</v>
+        <v>-9.1308260034307902e-05</v>
       </c>
       <c r="H14" s="1">
-        <v>0.00022584273992496128</v>
+        <v>0.00023201929755199566</v>
       </c>
       <c r="I14" s="1">
-        <v>0.00037898017835450538</v>
+        <v>0.00037998077714232454</v>
       </c>
       <c r="J14" s="1">
-        <v>0.00015165966043909713</v>
+        <v>0.00014965998320214571</v>
       </c>
       <c r="K14" s="1">
-        <v>0.0014688328919243879</v>
+        <v>0.0014708022138916952</v>
       </c>
       <c r="L14" s="1">
-        <v>0.00011589681868736889</v>
+        <v>0.00011730365898865387</v>
       </c>
       <c r="M14" s="1">
-        <v>0.002196204698253055</v>
+        <v>0.0022252340016767204</v>
       </c>
       <c r="N14" s="1">
-        <v>0.0032329483638377167</v>
+        <v>0.0032616717111737534</v>
       </c>
       <c r="O14" s="1">
-        <v>0.004784066477538638</v>
+        <v>0.0048137265733047795</v>
       </c>
       <c r="P14" s="1">
-        <v>0.0040721377041782565</v>
+        <v>0.0041035704210298672</v>
       </c>
       <c r="Q14" s="1">
-        <v>8.4513917106027441e-05</v>
+        <v>8.2164558511108043e-05</v>
       </c>
       <c r="R14" s="1">
-        <v>-0.00018943688572470118</v>
+        <v>-0.00018875661277092763</v>
       </c>
       <c r="S14" s="1">
-        <v>-6.8813556199373064e-05</v>
+        <v>-8.2031163788684534e-05</v>
       </c>
       <c r="T14" s="1">
-        <v>-0.00012934558008019935</v>
+        <v>-0.00012366178014785103</v>
       </c>
       <c r="U14" s="1">
-        <v>0.00068216161011721156</v>
+        <v>0.00068253757620718417</v>
       </c>
       <c r="V14" s="1">
-        <v>0.00017870981387129039</v>
+        <v>0.0001890270152713152</v>
       </c>
       <c r="W14" s="1">
-        <v>-0.00020519662887439878</v>
+        <v>-0.00020480199876988928</v>
       </c>
       <c r="X14" s="1">
-        <v>-0.00034851555977869408</v>
+        <v>-0.00034606084407912542</v>
       </c>
       <c r="Y14" s="1">
-        <v>-0.00024830620337586406</v>
+        <v>-0.00025013336638367051</v>
       </c>
       <c r="Z14" s="1">
-        <v>-9.1050100564592804e-05</v>
+        <v>-8.9342914562707371e-05</v>
       </c>
       <c r="AA14" s="1">
-        <v>3.6756876879519278e-05</v>
+        <v>3.6391221582812202e-05</v>
       </c>
       <c r="AB14" s="1">
-        <v>-0.00027649184603328067</v>
+        <v>-0.0002748439428099617</v>
       </c>
       <c r="AC14" s="1">
-        <v>-0.00038342776713306355</v>
+        <v>-0.00038551414231542214</v>
       </c>
       <c r="AD14" s="1">
-        <v>0.01202254955694416</v>
+        <v>0.011929009932283569</v>
       </c>
     </row>
     <row r="15">
@@ -3374,91 +3374,91 @@
         <v>40</v>
       </c>
       <c r="B15" s="1">
-        <v>-0.033166476710720982</v>
+        <v>-0.029738831894378336</v>
       </c>
       <c r="C15" s="1">
-        <v>6.3650887609722432e-06</v>
+        <v>2.8786150530319375e-06</v>
       </c>
       <c r="D15" s="1">
-        <v>-0.00040893668337514157</v>
+        <v>-0.00040697468991459165</v>
       </c>
       <c r="E15" s="1">
-        <v>3.6696851312948998e-06</v>
+        <v>3.6556982154547368e-06</v>
       </c>
       <c r="F15" s="1">
-        <v>-0.00019862245929399549</v>
+        <v>-0.00020286750977572404</v>
       </c>
       <c r="G15" s="1">
-        <v>-0.00015507968315515291</v>
+        <v>-0.00015421848968381587</v>
       </c>
       <c r="H15" s="1">
-        <v>0.00075483529409155496</v>
+        <v>0.00076125599964115204</v>
       </c>
       <c r="I15" s="1">
-        <v>0.00099592322559639975</v>
+        <v>0.00099708613078575018</v>
       </c>
       <c r="J15" s="1">
-        <v>-0.00021128741394695402</v>
+        <v>-0.00021334747518492788</v>
       </c>
       <c r="K15" s="1">
-        <v>0.0012372802067025339</v>
+        <v>0.0012393954563837324</v>
       </c>
       <c r="L15" s="1">
-        <v>0.00048883646339116765</v>
+        <v>0.00049028559032506425</v>
       </c>
       <c r="M15" s="1">
-        <v>0.0022013280760299053</v>
+        <v>0.0022336383737806354</v>
       </c>
       <c r="N15" s="1">
-        <v>0.003472752243249045</v>
+        <v>0.0035033137031109402</v>
       </c>
       <c r="O15" s="1">
-        <v>0.0040721377041782565</v>
+        <v>0.0041035704210298672</v>
       </c>
       <c r="P15" s="1">
-        <v>0.0055119218817725668</v>
+        <v>0.0055451710293080141</v>
       </c>
       <c r="Q15" s="1">
-        <v>0.00025946751597958023</v>
+        <v>0.00025707557950250523</v>
       </c>
       <c r="R15" s="1">
-        <v>-0.00013346095683912563</v>
+        <v>-0.00013301107353650058</v>
       </c>
       <c r="S15" s="1">
-        <v>-0.00016689268815104496</v>
+        <v>-0.00018022165237080649</v>
       </c>
       <c r="T15" s="1">
-        <v>-0.00010947174114196413</v>
+        <v>-0.00010403980897138113</v>
       </c>
       <c r="U15" s="1">
-        <v>0.0010194026317278022</v>
+        <v>0.0010199022248138518</v>
       </c>
       <c r="V15" s="1">
-        <v>0.00024487935538939818</v>
+        <v>0.00025540684970104424</v>
       </c>
       <c r="W15" s="1">
-        <v>-6.9491051968749266e-05</v>
+        <v>-6.8499637493662428e-05</v>
       </c>
       <c r="X15" s="1">
-        <v>-0.00016860090441877423</v>
+        <v>-0.00016582091556869574</v>
       </c>
       <c r="Y15" s="1">
-        <v>-9.743583090654213e-05</v>
+        <v>-9.8621686459467411e-05</v>
       </c>
       <c r="Z15" s="1">
-        <v>3.8059782892766101e-05</v>
+        <v>4.0393883376968611e-05</v>
       </c>
       <c r="AA15" s="1">
-        <v>3.1826016381666778e-05</v>
+        <v>3.1523376774181322e-05</v>
       </c>
       <c r="AB15" s="1">
-        <v>-0.00016244636342382251</v>
+        <v>-0.0001612451690773647</v>
       </c>
       <c r="AC15" s="1">
-        <v>-0.00018697354235369093</v>
+        <v>-0.00018937024744497468</v>
       </c>
       <c r="AD15" s="1">
-        <v>0.0054388672817952885</v>
+        <v>0.0053418272320886369</v>
       </c>
     </row>
     <row r="16">
@@ -3466,91 +3466,91 @@
         <v>41</v>
       </c>
       <c r="B16" s="1">
-        <v>-0.16862319296297823</v>
+        <v>-0.16867782734234921</v>
       </c>
       <c r="C16" s="1">
-        <v>-0.00069754342896915069</v>
+        <v>-0.00069705987500229532</v>
       </c>
       <c r="D16" s="1">
-        <v>0.00023924200194067741</v>
+        <v>0.00024036456956684146</v>
       </c>
       <c r="E16" s="1">
-        <v>-1.6842521293228784e-06</v>
+        <v>-1.6944316605496993e-06</v>
       </c>
       <c r="F16" s="1">
-        <v>4.2506254764311524e-05</v>
+        <v>4.2583379924906323e-05</v>
       </c>
       <c r="G16" s="1">
-        <v>-4.2584902731655945e-05</v>
+        <v>-4.2248131494016135e-05</v>
       </c>
       <c r="H16" s="1">
-        <v>-9.4509089046827311e-06</v>
+        <v>-9.6837172638545611e-06</v>
       </c>
       <c r="I16" s="1">
-        <v>0.00014269493493104655</v>
+        <v>0.00014240229746623391</v>
       </c>
       <c r="J16" s="1">
-        <v>-0.00041794680650147258</v>
+        <v>-0.00041706959052231567</v>
       </c>
       <c r="K16" s="1">
-        <v>-0.0011882352697712467</v>
+        <v>-0.0011874621532563057</v>
       </c>
       <c r="L16" s="1">
-        <v>6.8904080738087497e-06</v>
+        <v>6.1280332287918084e-06</v>
       </c>
       <c r="M16" s="1">
-        <v>0.00020701937767074872</v>
+        <v>0.00020103124865936389</v>
       </c>
       <c r="N16" s="1">
-        <v>0.00017006508000365033</v>
+        <v>0.00016782071755349584</v>
       </c>
       <c r="O16" s="1">
-        <v>8.4513917106027441e-05</v>
+        <v>8.2164558511108043e-05</v>
       </c>
       <c r="P16" s="1">
-        <v>0.00025946751597958023</v>
+        <v>0.00025707557950250523</v>
       </c>
       <c r="Q16" s="1">
-        <v>0.002526429650611688</v>
+        <v>0.0025251955138734603</v>
       </c>
       <c r="R16" s="1">
-        <v>-7.4343200316118662e-05</v>
+        <v>-7.3721368257334031e-05</v>
       </c>
       <c r="S16" s="1">
-        <v>-0.00013414659348528818</v>
+        <v>-0.00013494818488928441</v>
       </c>
       <c r="T16" s="1">
-        <v>-0.00010082430944920498</v>
+        <v>-0.00010013498392631395</v>
       </c>
       <c r="U16" s="1">
-        <v>0.00019361154137520703</v>
+        <v>0.00019352809341860629</v>
       </c>
       <c r="V16" s="1">
-        <v>-8.8630353623481758e-05</v>
+        <v>-8.9051345566047496e-05</v>
       </c>
       <c r="W16" s="1">
-        <v>1.734079080628571e-05</v>
+        <v>1.6969315041571748e-05</v>
       </c>
       <c r="X16" s="1">
-        <v>7.2270049866705204e-05</v>
+        <v>7.1739782280402266e-05</v>
       </c>
       <c r="Y16" s="1">
-        <v>0.00016128783540288053</v>
+        <v>0.00016066130479702213</v>
       </c>
       <c r="Z16" s="1">
-        <v>-3.9133756307044233e-05</v>
+        <v>-3.9273264754122747e-05</v>
       </c>
       <c r="AA16" s="1">
-        <v>-4.9745257221354316e-06</v>
+        <v>-5.0478514700682208e-06</v>
       </c>
       <c r="AB16" s="1">
-        <v>5.1103307073509241e-05</v>
+        <v>5.0658485755169895e-05</v>
       </c>
       <c r="AC16" s="1">
-        <v>0.0001023096100071022</v>
+        <v>0.00010276410766520833</v>
       </c>
       <c r="AD16" s="1">
-        <v>-0.0078578532581113567</v>
+        <v>-0.0078850728970835185</v>
       </c>
     </row>
     <row r="17">
@@ -3558,91 +3558,91 @@
         <v>51</v>
       </c>
       <c r="B17" s="1">
-        <v>0.0030510245078998648</v>
+        <v>0.0030475020337151315</v>
       </c>
       <c r="C17" s="1">
-        <v>8.4262788811329068e-05</v>
+        <v>8.4081874091737748e-05</v>
       </c>
       <c r="D17" s="1">
-        <v>0.0003912964687543645</v>
+        <v>0.0003903885445184184</v>
       </c>
       <c r="E17" s="1">
-        <v>-4.1542477240590948e-06</v>
+        <v>-4.146521257258857e-06</v>
       </c>
       <c r="F17" s="1">
-        <v>-0.00040748308329207651</v>
+        <v>-0.00040709119719720913</v>
       </c>
       <c r="G17" s="1">
-        <v>-0.00041320111576919737</v>
+        <v>-0.00041339875495975328</v>
       </c>
       <c r="H17" s="1">
-        <v>0.00013469660076571624</v>
+        <v>0.00013407976979868354</v>
       </c>
       <c r="I17" s="1">
-        <v>0.0001166578478593224</v>
+        <v>0.00011627824684830692</v>
       </c>
       <c r="J17" s="1">
-        <v>-0.00011973231116640753</v>
+        <v>-0.00012012337938340905</v>
       </c>
       <c r="K17" s="1">
-        <v>-7.4251394028742473e-05</v>
+        <v>-7.4548379598208083e-05</v>
       </c>
       <c r="L17" s="1">
-        <v>0.00012300619782789159</v>
+        <v>0.00012331879840838468</v>
       </c>
       <c r="M17" s="1">
-        <v>-0.00016997608527821563</v>
+        <v>-0.00016714156273139939</v>
       </c>
       <c r="N17" s="1">
-        <v>8.7274665589687293e-05</v>
+        <v>8.7945962661358152e-05</v>
       </c>
       <c r="O17" s="1">
-        <v>-0.00018943688572470118</v>
+        <v>-0.00018875661277092763</v>
       </c>
       <c r="P17" s="1">
-        <v>-0.00013346095683912563</v>
+        <v>-0.00013301107353650058</v>
       </c>
       <c r="Q17" s="1">
-        <v>-7.4343200316118662e-05</v>
+        <v>-7.3721368257334031e-05</v>
       </c>
       <c r="R17" s="1">
-        <v>0.0021436484767034508</v>
+        <v>0.0021433492067214613</v>
       </c>
       <c r="S17" s="1">
-        <v>-0.00044148476225812952</v>
+        <v>-0.00044093403530706145</v>
       </c>
       <c r="T17" s="1">
-        <v>-0.00026186244635291922</v>
+        <v>-0.00026204253086419156</v>
       </c>
       <c r="U17" s="1">
-        <v>-0.00038188090454154911</v>
+        <v>-0.0003817291546846417</v>
       </c>
       <c r="V17" s="1">
-        <v>0.00028394201137188317</v>
+        <v>0.00028346758051652724</v>
       </c>
       <c r="W17" s="1">
-        <v>-3.8691548839904499e-05</v>
+        <v>-3.850760687911306e-05</v>
       </c>
       <c r="X17" s="1">
-        <v>2.8355957939426169e-05</v>
+        <v>2.8601949746123007e-05</v>
       </c>
       <c r="Y17" s="1">
-        <v>-7.2730882252180617e-06</v>
+        <v>-6.8327509776262407e-06</v>
       </c>
       <c r="Z17" s="1">
-        <v>0.00011725711972378135</v>
+        <v>0.00011738693263587486</v>
       </c>
       <c r="AA17" s="1">
-        <v>-1.3059324755440623e-05</v>
+        <v>-1.3012514249033646e-05</v>
       </c>
       <c r="AB17" s="1">
-        <v>-1.492716288944854e-05</v>
+        <v>-1.4657399582020635e-05</v>
       </c>
       <c r="AC17" s="1">
-        <v>0.00064916580668317658</v>
+        <v>0.0006490742623075545</v>
       </c>
       <c r="AD17" s="1">
-        <v>-0.0086988509029209248</v>
+        <v>-0.0086732506916401813</v>
       </c>
     </row>
     <row r="18">
@@ -3650,91 +3650,91 @@
         <v>52</v>
       </c>
       <c r="B18" s="1">
-        <v>0.11228971480239665</v>
+        <v>0.11221172818292792</v>
       </c>
       <c r="C18" s="1">
-        <v>0.00064089701780007768</v>
+        <v>0.00064111944641499329</v>
       </c>
       <c r="D18" s="1">
-        <v>-0.00082936790661555272</v>
+        <v>-0.00082849223526633084</v>
       </c>
       <c r="E18" s="1">
-        <v>6.9433638656307321e-06</v>
+        <v>6.935389507512304e-06</v>
       </c>
       <c r="F18" s="1">
-        <v>0.00027582664246725676</v>
+        <v>0.00027594476830014938</v>
       </c>
       <c r="G18" s="1">
-        <v>0.00024156228234947048</v>
+        <v>0.00024173667028505423</v>
       </c>
       <c r="H18" s="1">
-        <v>-1.3740734714760779e-05</v>
+        <v>-1.39000627221119e-05</v>
       </c>
       <c r="I18" s="1">
-        <v>-0.00012874124670425572</v>
+        <v>-0.00012859858556031891</v>
       </c>
       <c r="J18" s="1">
-        <v>-0.00013056200243810774</v>
+        <v>-0.00012945392406336017</v>
       </c>
       <c r="K18" s="1">
-        <v>-1.734992209942687e-05</v>
+        <v>-1.7176389620661214e-05</v>
       </c>
       <c r="L18" s="1">
-        <v>8.9771476946931309e-05</v>
+        <v>8.8555117112579923e-05</v>
       </c>
       <c r="M18" s="1">
-        <v>0.00012971782276768214</v>
+        <v>0.00010439556845814558</v>
       </c>
       <c r="N18" s="1">
-        <v>-0.00014419974736451776</v>
+        <v>-0.00015715895350435134</v>
       </c>
       <c r="O18" s="1">
-        <v>-6.8813556199373064e-05</v>
+        <v>-8.2031163788684534e-05</v>
       </c>
       <c r="P18" s="1">
-        <v>-0.00016689268815104496</v>
+        <v>-0.00018022165237080649</v>
       </c>
       <c r="Q18" s="1">
-        <v>-0.00013414659348528818</v>
+        <v>-0.00013494818488928441</v>
       </c>
       <c r="R18" s="1">
-        <v>-0.00044148476225812952</v>
+        <v>-0.00044093403530706145</v>
       </c>
       <c r="S18" s="1">
-        <v>0.0040839288574837391</v>
+        <v>0.0040822595142384049</v>
       </c>
       <c r="T18" s="1">
-        <v>0.00091035746708560434</v>
+        <v>0.00091029083332136603</v>
       </c>
       <c r="U18" s="1">
-        <v>0.00010389163151704444</v>
+        <v>0.0001033105819263332</v>
       </c>
       <c r="V18" s="1">
-        <v>-0.00018871098183299633</v>
+        <v>-0.00018892495181351693</v>
       </c>
       <c r="W18" s="1">
-        <v>-3.5622354587015043e-07</v>
+        <v>-4.1437896289905213e-07</v>
       </c>
       <c r="X18" s="1">
-        <v>-0.00012961231160109137</v>
+        <v>-0.00012980534661323029</v>
       </c>
       <c r="Y18" s="1">
-        <v>4.4730034432408951e-05</v>
+        <v>4.4195838948062408e-05</v>
       </c>
       <c r="Z18" s="1">
-        <v>-3.2969213911123721e-05</v>
+        <v>-3.3204122728909286e-05</v>
       </c>
       <c r="AA18" s="1">
-        <v>-9.5435930494038967e-06</v>
+        <v>-9.641698970085761e-06</v>
       </c>
       <c r="AB18" s="1">
-        <v>9.1980204965572479e-05</v>
+        <v>9.2372222803047133e-05</v>
       </c>
       <c r="AC18" s="1">
-        <v>-0.00013415981922260643</v>
+        <v>-0.00013325197260220453</v>
       </c>
       <c r="AD18" s="1">
-        <v>0.024348328183547582</v>
+        <v>0.024339460960430971</v>
       </c>
     </row>
     <row r="19">
@@ -3742,91 +3742,91 @@
         <v>53</v>
       </c>
       <c r="B19" s="1">
-        <v>0.14427479119321079</v>
+        <v>0.14430474222648718</v>
       </c>
       <c r="C19" s="1">
-        <v>0.0006114966993194319</v>
+        <v>0.00061150156097970819</v>
       </c>
       <c r="D19" s="1">
-        <v>-0.00081423433782255774</v>
+        <v>-0.00081414227336978028</v>
       </c>
       <c r="E19" s="1">
-        <v>6.7904105808029526e-06</v>
+        <v>6.7898444520005528e-06</v>
       </c>
       <c r="F19" s="1">
-        <v>0.00029943046820353741</v>
+        <v>0.0002990988169313878</v>
       </c>
       <c r="G19" s="1">
-        <v>0.00022219611793040613</v>
+        <v>0.00022213145078145099</v>
       </c>
       <c r="H19" s="1">
-        <v>-7.8623942769521219e-05</v>
+        <v>-7.984045103867018e-05</v>
       </c>
       <c r="I19" s="1">
-        <v>2.7953952769162768e-06</v>
+        <v>1.5055522240919005e-06</v>
       </c>
       <c r="J19" s="1">
-        <v>-0.00026544081782506747</v>
+        <v>-0.00026558822653842163</v>
       </c>
       <c r="K19" s="1">
-        <v>8.1879965698179551e-05</v>
+        <v>8.1979349749285464e-05</v>
       </c>
       <c r="L19" s="1">
-        <v>-6.2234975630878414e-05</v>
+        <v>-6.2088709636105364e-05</v>
       </c>
       <c r="M19" s="1">
-        <v>4.6936817608976696e-05</v>
+        <v>5.6099798986346735e-05</v>
       </c>
       <c r="N19" s="1">
-        <v>-0.00017695988687609483</v>
+        <v>-0.00017134504534634093</v>
       </c>
       <c r="O19" s="1">
-        <v>-0.00012934558008019935</v>
+        <v>-0.00012366178014785103</v>
       </c>
       <c r="P19" s="1">
-        <v>-0.00010947174114196413</v>
+        <v>-0.00010403980897138113</v>
       </c>
       <c r="Q19" s="1">
-        <v>-0.00010082430944920498</v>
+        <v>-0.00010013498392631395</v>
       </c>
       <c r="R19" s="1">
-        <v>-0.00026186244635291922</v>
+        <v>-0.00026204253086419156</v>
       </c>
       <c r="S19" s="1">
-        <v>0.00091035746708560434</v>
+        <v>0.00091029083332136603</v>
       </c>
       <c r="T19" s="1">
-        <v>0.0044753352501089756</v>
+        <v>0.0044744252047934693</v>
       </c>
       <c r="U19" s="1">
-        <v>4.886654832518024e-05</v>
+        <v>4.8919688965351482e-05</v>
       </c>
       <c r="V19" s="1">
-        <v>-0.00023050093667664057</v>
+        <v>-0.00022955196487558409</v>
       </c>
       <c r="W19" s="1">
-        <v>-9.6491705341355399e-05</v>
+        <v>-9.648693258296117e-05</v>
       </c>
       <c r="X19" s="1">
-        <v>-3.6874960806408934e-05</v>
+        <v>-3.6819180722024152e-05</v>
       </c>
       <c r="Y19" s="1">
-        <v>-4.7195282076966695e-05</v>
+        <v>-4.7116860160298715e-05</v>
       </c>
       <c r="Z19" s="1">
-        <v>-4.9164895277617211e-05</v>
+        <v>-4.9143908134775252e-05</v>
       </c>
       <c r="AA19" s="1">
-        <v>4.2975644553293769e-06</v>
+        <v>4.3237137240494583e-06</v>
       </c>
       <c r="AB19" s="1">
-        <v>-2.541767607558594e-05</v>
+        <v>-2.5645370190762948e-05</v>
       </c>
       <c r="AC19" s="1">
-        <v>-0.00013737641915654263</v>
+        <v>-0.0001378291281680117</v>
       </c>
       <c r="AD19" s="1">
-        <v>0.02386382796649171</v>
+        <v>0.023855413407898998</v>
       </c>
     </row>
     <row r="20">
@@ -3834,91 +3834,91 @@
         <v>54</v>
       </c>
       <c r="B20" s="1">
-        <v>0.097262821325371951</v>
+        <v>0.097365203302091641</v>
       </c>
       <c r="C20" s="1">
-        <v>1.3775632837375327e-05</v>
+        <v>1.3756852253357047e-05</v>
       </c>
       <c r="D20" s="1">
-        <v>5.9748764067758808e-06</v>
+        <v>5.9998282366802158e-06</v>
       </c>
       <c r="E20" s="1">
-        <v>-8.1450508840141085e-08</v>
+        <v>-8.1543469037379575e-08</v>
       </c>
       <c r="F20" s="1">
-        <v>-0.00012530015091925199</v>
+        <v>-0.00012545708909244765</v>
       </c>
       <c r="G20" s="1">
-        <v>-0.00021874024278582729</v>
+        <v>-0.00021874189018649716</v>
       </c>
       <c r="H20" s="1">
-        <v>8.7984862407354314e-05</v>
+        <v>8.8645211204724245e-05</v>
       </c>
       <c r="I20" s="1">
-        <v>1.6699583377934729e-05</v>
+        <v>1.716506834285739e-05</v>
       </c>
       <c r="J20" s="1">
-        <v>-0.00024503968109940768</v>
+        <v>-0.0002449540754716995</v>
       </c>
       <c r="K20" s="1">
-        <v>-0.00013564933317826016</v>
+        <v>-0.00013550568942595245</v>
       </c>
       <c r="L20" s="1">
-        <v>0.0003638498635348257</v>
+        <v>0.0003636152840151588</v>
       </c>
       <c r="M20" s="1">
-        <v>2.3557686489050344e-05</v>
+        <v>2.4484113650679814e-05</v>
       </c>
       <c r="N20" s="1">
-        <v>0.00073173858196808289</v>
+        <v>0.00073213020111707297</v>
       </c>
       <c r="O20" s="1">
-        <v>0.00068216161011721156</v>
+        <v>0.00068253757620718417</v>
       </c>
       <c r="P20" s="1">
-        <v>0.0010194026317278022</v>
+        <v>0.0010199022248138518</v>
       </c>
       <c r="Q20" s="1">
-        <v>0.00019361154137520703</v>
+        <v>0.00019352809341860629</v>
       </c>
       <c r="R20" s="1">
-        <v>-0.00038188090454154911</v>
+        <v>-0.0003817291546846417</v>
       </c>
       <c r="S20" s="1">
-        <v>0.00010389163151704444</v>
+        <v>0.0001033105819263332</v>
       </c>
       <c r="T20" s="1">
-        <v>4.886654832518024e-05</v>
+        <v>4.8919688965351482e-05</v>
       </c>
       <c r="U20" s="1">
-        <v>0.0016139099301116847</v>
+        <v>0.0016136373349336969</v>
       </c>
       <c r="V20" s="1">
-        <v>-0.00077214181312352734</v>
+        <v>-0.00077193140232018433</v>
       </c>
       <c r="W20" s="1">
-        <v>-3.9199592089404593e-05</v>
+        <v>-3.9155012261898664e-05</v>
       </c>
       <c r="X20" s="1">
-        <v>-0.00013532422625973987</v>
+        <v>-0.00013522294718472695</v>
       </c>
       <c r="Y20" s="1">
-        <v>-6.3212841821651006e-05</v>
+        <v>-6.311038794686941e-05</v>
       </c>
       <c r="Z20" s="1">
-        <v>0.00020545198786285846</v>
+        <v>0.00020550543764172378</v>
       </c>
       <c r="AA20" s="1">
-        <v>1.2871512275885922e-05</v>
+        <v>1.2863852309415809e-05</v>
       </c>
       <c r="AB20" s="1">
-        <v>3.357832726139532e-05</v>
+        <v>3.3631820408682508e-05</v>
       </c>
       <c r="AC20" s="1">
-        <v>0.00024068360065520895</v>
+        <v>0.00024050821418075772</v>
       </c>
       <c r="AD20" s="1">
-        <v>-0.0016057612810675605</v>
+        <v>-0.001607758475009196</v>
       </c>
     </row>
     <row r="21">
@@ -3926,91 +3926,91 @@
         <v>55</v>
       </c>
       <c r="B21" s="1">
-        <v>0.047105190428660793</v>
+        <v>0.047132450469209199</v>
       </c>
       <c r="C21" s="1">
-        <v>3.6419482317014877e-05</v>
+        <v>3.6395070718797619e-05</v>
       </c>
       <c r="D21" s="1">
-        <v>-0.00015052663880638431</v>
+        <v>-0.00014937979534815349</v>
       </c>
       <c r="E21" s="1">
-        <v>1.339236452010717e-06</v>
+        <v>1.3300668113350449e-06</v>
       </c>
       <c r="F21" s="1">
-        <v>-4.1666978713212136e-05</v>
+        <v>-4.2942995505832957e-05</v>
       </c>
       <c r="G21" s="1">
-        <v>0.00018414739386359881</v>
+        <v>0.00018370270405850073</v>
       </c>
       <c r="H21" s="1">
-        <v>3.4630650701491291e-05</v>
+        <v>3.5420483081301127e-05</v>
       </c>
       <c r="I21" s="1">
-        <v>-2.4130707402652543e-05</v>
+        <v>-2.3698774530202076e-05</v>
       </c>
       <c r="J21" s="1">
-        <v>0.0002319188340691472</v>
+        <v>0.00023178251570455137</v>
       </c>
       <c r="K21" s="1">
-        <v>0.00037540304085696398</v>
+        <v>0.00037548087850716109</v>
       </c>
       <c r="L21" s="1">
-        <v>-0.0003331633263491752</v>
+        <v>-0.00033280467288483804</v>
       </c>
       <c r="M21" s="1">
-        <v>0.00033157118438130006</v>
+        <v>0.00034756903216696239</v>
       </c>
       <c r="N21" s="1">
-        <v>-9.2917665589716133e-05</v>
+        <v>-8.2709880215469289e-05</v>
       </c>
       <c r="O21" s="1">
-        <v>0.00017870981387129039</v>
+        <v>0.0001890270152713152</v>
       </c>
       <c r="P21" s="1">
-        <v>0.00024487935538939818</v>
+        <v>0.00025540684970104424</v>
       </c>
       <c r="Q21" s="1">
-        <v>-8.8630353623481758e-05</v>
+        <v>-8.9051345566047496e-05</v>
       </c>
       <c r="R21" s="1">
-        <v>0.00028394201137188317</v>
+        <v>0.00028346758051652724</v>
       </c>
       <c r="S21" s="1">
-        <v>-0.00018871098183299633</v>
+        <v>-0.00018892495181351693</v>
       </c>
       <c r="T21" s="1">
-        <v>-0.00023050093667664057</v>
+        <v>-0.00022955196487558409</v>
       </c>
       <c r="U21" s="1">
-        <v>-0.00077214181312352734</v>
+        <v>-0.00077193140232018433</v>
       </c>
       <c r="V21" s="1">
-        <v>0.0029813486962245363</v>
+        <v>0.0029828902420442035</v>
       </c>
       <c r="W21" s="1">
-        <v>2.2710794892574402e-05</v>
+        <v>2.2639894526378613e-05</v>
       </c>
       <c r="X21" s="1">
-        <v>0.0001760233740489472</v>
+        <v>0.00017626146455338961</v>
       </c>
       <c r="Y21" s="1">
-        <v>-3.1660862198888543e-05</v>
+        <v>-3.2233234668460988e-05</v>
       </c>
       <c r="Z21" s="1">
-        <v>-0.00015321791538404719</v>
+        <v>-0.00015284062817122655</v>
       </c>
       <c r="AA21" s="1">
-        <v>-6.6639905679296977e-06</v>
+        <v>-6.6326452828944536e-06</v>
       </c>
       <c r="AB21" s="1">
-        <v>1.5822208045967795e-05</v>
+        <v>1.4673078924287231e-05</v>
       </c>
       <c r="AC21" s="1">
-        <v>-0.00014268924060088957</v>
+        <v>-0.00014357349765222772</v>
       </c>
       <c r="AD21" s="1">
-        <v>0.0040286680793748357</v>
+        <v>0.0039818438517078619</v>
       </c>
     </row>
     <row r="22">
@@ -4018,91 +4018,91 @@
         <v>42</v>
       </c>
       <c r="B22" s="1">
-        <v>-0.14241021326791037</v>
+        <v>-0.1423757451107921</v>
       </c>
       <c r="C22" s="1">
-        <v>-0.00031636551779414294</v>
+        <v>-0.00031625325709478758</v>
       </c>
       <c r="D22" s="1">
-        <v>0.00027940960703747714</v>
+        <v>0.0002794308690572192</v>
       </c>
       <c r="E22" s="1">
-        <v>-1.955251280088958e-06</v>
+        <v>-1.9553974809714131e-06</v>
       </c>
       <c r="F22" s="1">
-        <v>0.00011242442893759884</v>
+        <v>0.00011233181646577196</v>
       </c>
       <c r="G22" s="1">
-        <v>2.9470276791886477e-05</v>
+        <v>2.9563091247094761e-05</v>
       </c>
       <c r="H22" s="1">
-        <v>9.2133671906330589e-05</v>
+        <v>9.424261472959993e-05</v>
       </c>
       <c r="I22" s="1">
-        <v>-5.2400507175013765e-05</v>
+        <v>-5.0397281129728206e-05</v>
       </c>
       <c r="J22" s="1">
-        <v>-0.00030843252272358222</v>
+        <v>-0.00030815426234148099</v>
       </c>
       <c r="K22" s="1">
-        <v>-0.00025011880627297093</v>
+        <v>-0.00025000183947172902</v>
       </c>
       <c r="L22" s="1">
-        <v>0.00014704362225899744</v>
+        <v>0.00014685493987238074</v>
       </c>
       <c r="M22" s="1">
-        <v>2.6077675107084495e-05</v>
+        <v>2.6669175055226498e-05</v>
       </c>
       <c r="N22" s="1">
-        <v>-9.1689557595698505e-05</v>
+        <v>-9.1350099976601567e-05</v>
       </c>
       <c r="O22" s="1">
-        <v>-0.00020519662887439878</v>
+        <v>-0.00020480199876988928</v>
       </c>
       <c r="P22" s="1">
-        <v>-6.9491051968749266e-05</v>
+        <v>-6.8499637493662428e-05</v>
       </c>
       <c r="Q22" s="1">
-        <v>1.734079080628571e-05</v>
+        <v>1.6969315041571748e-05</v>
       </c>
       <c r="R22" s="1">
-        <v>-3.8691548839904499e-05</v>
+        <v>-3.850760687911306e-05</v>
       </c>
       <c r="S22" s="1">
-        <v>-3.5622354587015043e-07</v>
+        <v>-4.1437896289905213e-07</v>
       </c>
       <c r="T22" s="1">
-        <v>-9.6491705341355399e-05</v>
+        <v>-9.648693258296117e-05</v>
       </c>
       <c r="U22" s="1">
-        <v>-3.9199592089404593e-05</v>
+        <v>-3.9155012261898664e-05</v>
       </c>
       <c r="V22" s="1">
-        <v>2.2710794892574402e-05</v>
+        <v>2.2639894526378613e-05</v>
       </c>
       <c r="W22" s="1">
-        <v>0.0025463192024388695</v>
+        <v>0.0025463361364869638</v>
       </c>
       <c r="X22" s="1">
-        <v>0.0013927330608175523</v>
+        <v>0.0013926367725228754</v>
       </c>
       <c r="Y22" s="1">
-        <v>0.0013641977861016611</v>
+        <v>0.0013640561435717053</v>
       </c>
       <c r="Z22" s="1">
-        <v>0.0013745225970127901</v>
+        <v>0.0013745221907014776</v>
       </c>
       <c r="AA22" s="1">
-        <v>-3.5154885553137624e-05</v>
+        <v>-3.5140600144635152e-05</v>
       </c>
       <c r="AB22" s="1">
-        <v>0.00027587382848206067</v>
+        <v>0.00027565371357394142</v>
       </c>
       <c r="AC22" s="1">
-        <v>9.2553600992713162e-05</v>
+        <v>9.2578720705362529e-05</v>
       </c>
       <c r="AD22" s="1">
-        <v>-0.010062623184785695</v>
+        <v>-0.010066095472931656</v>
       </c>
     </row>
     <row r="23">
@@ -4110,91 +4110,91 @@
         <v>43</v>
       </c>
       <c r="B23" s="1">
-        <v>0.0070839787570477807</v>
+        <v>0.0071445184628676373</v>
       </c>
       <c r="C23" s="1">
-        <v>-0.00014499133940875926</v>
+        <v>-0.00014466675143836758</v>
       </c>
       <c r="D23" s="1">
-        <v>0.00013153047600365786</v>
+        <v>0.00013170998465468486</v>
       </c>
       <c r="E23" s="1">
-        <v>-1.0118871289766911e-06</v>
+        <v>-1.013769504586189e-06</v>
       </c>
       <c r="F23" s="1">
-        <v>8.0661687157407031e-05</v>
+        <v>8.037196471648864e-05</v>
       </c>
       <c r="G23" s="1">
-        <v>0.00015162865180272291</v>
+        <v>0.00015183067948679641</v>
       </c>
       <c r="H23" s="1">
-        <v>0.00017296126625769364</v>
+        <v>0.0001737357466902442</v>
       </c>
       <c r="I23" s="1">
-        <v>0.00011938926591684692</v>
+        <v>0.00012017143654060234</v>
       </c>
       <c r="J23" s="1">
-        <v>-9.3671063306771763e-05</v>
+        <v>-9.3192080305325078e-05</v>
       </c>
       <c r="K23" s="1">
-        <v>-0.00017278947335544099</v>
+        <v>-0.00017246788388097448</v>
       </c>
       <c r="L23" s="1">
-        <v>1.7358690679364781e-05</v>
+        <v>1.7342659240487284e-05</v>
       </c>
       <c r="M23" s="1">
-        <v>0.00010795880567861864</v>
+        <v>0.00011171655575287036</v>
       </c>
       <c r="N23" s="1">
-        <v>-0.00021504076679775336</v>
+        <v>-0.00021260949092050623</v>
       </c>
       <c r="O23" s="1">
-        <v>-0.00034851555977869408</v>
+        <v>-0.00034606084407912542</v>
       </c>
       <c r="P23" s="1">
-        <v>-0.00016860090441877423</v>
+        <v>-0.00016582091556869574</v>
       </c>
       <c r="Q23" s="1">
-        <v>7.2270049866705204e-05</v>
+        <v>7.1739782280402266e-05</v>
       </c>
       <c r="R23" s="1">
-        <v>2.8355957939426169e-05</v>
+        <v>2.8601949746123007e-05</v>
       </c>
       <c r="S23" s="1">
-        <v>-0.00012961231160109137</v>
+        <v>-0.00012980534661323029</v>
       </c>
       <c r="T23" s="1">
-        <v>-3.6874960806408934e-05</v>
+        <v>-3.6819180722024152e-05</v>
       </c>
       <c r="U23" s="1">
-        <v>-0.00013532422625973987</v>
+        <v>-0.00013522294718472695</v>
       </c>
       <c r="V23" s="1">
-        <v>0.0001760233740489472</v>
+        <v>0.00017626146455338961</v>
       </c>
       <c r="W23" s="1">
-        <v>0.0013927330608175523</v>
+        <v>0.0013926367725228754</v>
       </c>
       <c r="X23" s="1">
-        <v>0.0038837143181447236</v>
+        <v>0.0038837128638420232</v>
       </c>
       <c r="Y23" s="1">
-        <v>0.001386042355472262</v>
+        <v>0.0013857956088977918</v>
       </c>
       <c r="Z23" s="1">
-        <v>0.0014049456939183788</v>
+        <v>0.001404971446223182</v>
       </c>
       <c r="AA23" s="1">
-        <v>-1.9269722479712451e-05</v>
+        <v>-1.9271698944529365e-05</v>
       </c>
       <c r="AB23" s="1">
-        <v>9.7761048059906886e-05</v>
+        <v>9.7384612483604038e-05</v>
       </c>
       <c r="AC23" s="1">
-        <v>-1.5845446025822838e-05</v>
+        <v>-1.5983978684886943e-05</v>
       </c>
       <c r="AD23" s="1">
-        <v>-0.0050539260787616867</v>
+        <v>-0.0050614973152840591</v>
       </c>
     </row>
     <row r="24">
@@ -4202,91 +4202,91 @@
         <v>44</v>
       </c>
       <c r="B24" s="1">
-        <v>-0.082487304521523003</v>
+        <v>-0.08243990689586092</v>
       </c>
       <c r="C24" s="1">
-        <v>-0.0002349981681333789</v>
+        <v>-0.0002347743718051137</v>
       </c>
       <c r="D24" s="1">
-        <v>0.00031990649440274271</v>
+        <v>0.00032016539832730589</v>
       </c>
       <c r="E24" s="1">
-        <v>-2.3239462200045692e-06</v>
+        <v>-2.3264625613003296e-06</v>
       </c>
       <c r="F24" s="1">
-        <v>-8.6648802190905649e-06</v>
+        <v>-8.8147579414155769e-06</v>
       </c>
       <c r="G24" s="1">
-        <v>-1.326514163258255e-06</v>
+        <v>-1.2081151540745821e-06</v>
       </c>
       <c r="H24" s="1">
-        <v>0.00015930161468260249</v>
+        <v>0.00016151554315779585</v>
       </c>
       <c r="I24" s="1">
-        <v>3.630845010161492e-05</v>
+        <v>3.8517321355710987e-05</v>
       </c>
       <c r="J24" s="1">
-        <v>-0.0002765266385888093</v>
+        <v>-0.00027580934530650167</v>
       </c>
       <c r="K24" s="1">
-        <v>-0.0002913559535498415</v>
+        <v>-0.0002909556186508085</v>
       </c>
       <c r="L24" s="1">
-        <v>0.00010927461134957602</v>
+        <v>0.00010871025376677954</v>
       </c>
       <c r="M24" s="1">
-        <v>8.0453958298756182e-05</v>
+        <v>7.6164394857071828e-05</v>
       </c>
       <c r="N24" s="1">
-        <v>-0.00011389947680730429</v>
+        <v>-0.00011576996550806721</v>
       </c>
       <c r="O24" s="1">
-        <v>-0.00024830620337586406</v>
+        <v>-0.00025013336638367051</v>
       </c>
       <c r="P24" s="1">
-        <v>-9.743583090654213e-05</v>
+        <v>-9.8621686459467411e-05</v>
       </c>
       <c r="Q24" s="1">
-        <v>0.00016128783540288053</v>
+        <v>0.00016066130479702213</v>
       </c>
       <c r="R24" s="1">
-        <v>-7.2730882252180617e-06</v>
+        <v>-6.8327509776262407e-06</v>
       </c>
       <c r="S24" s="1">
-        <v>4.4730034432408951e-05</v>
+        <v>4.4195838948062408e-05</v>
       </c>
       <c r="T24" s="1">
-        <v>-4.7195282076966695e-05</v>
+        <v>-4.7116860160298715e-05</v>
       </c>
       <c r="U24" s="1">
-        <v>-6.3212841821651006e-05</v>
+        <v>-6.311038794686941e-05</v>
       </c>
       <c r="V24" s="1">
-        <v>-3.1660862198888543e-05</v>
+        <v>-3.2233234668460988e-05</v>
       </c>
       <c r="W24" s="1">
-        <v>0.0013641977861016611</v>
+        <v>0.0013640561435717053</v>
       </c>
       <c r="X24" s="1">
-        <v>0.001386042355472262</v>
+        <v>0.0013857956088977918</v>
       </c>
       <c r="Y24" s="1">
-        <v>0.0025664864140428965</v>
+        <v>0.0025660396969312623</v>
       </c>
       <c r="Z24" s="1">
-        <v>0.0013649968172642481</v>
+        <v>0.0013648891338309563</v>
       </c>
       <c r="AA24" s="1">
-        <v>-3.6164782152594287e-05</v>
+        <v>-3.6182728925014593e-05</v>
       </c>
       <c r="AB24" s="1">
-        <v>0.00024612535088614342</v>
+        <v>0.0002459935930858883</v>
       </c>
       <c r="AC24" s="1">
-        <v>0.00024967563655823265</v>
+        <v>0.00025019692448735597</v>
       </c>
       <c r="AD24" s="1">
-        <v>-0.011223569844145683</v>
+        <v>-0.01123029636373969</v>
       </c>
     </row>
     <row r="25">
@@ -4294,91 +4294,91 @@
         <v>45</v>
       </c>
       <c r="B25" s="1">
-        <v>-0.069616665618571924</v>
+        <v>-0.069523696879727953</v>
       </c>
       <c r="C25" s="1">
-        <v>-0.00014321333190522639</v>
+        <v>-0.0001431394394607211</v>
       </c>
       <c r="D25" s="1">
-        <v>0.00032568306113439638</v>
+        <v>0.00032583794046796809</v>
       </c>
       <c r="E25" s="1">
-        <v>-2.4783066057005307e-06</v>
+        <v>-2.4794692075943287e-06</v>
       </c>
       <c r="F25" s="1">
-        <v>-0.00010666944760849778</v>
+        <v>-0.00010688810083355404</v>
       </c>
       <c r="G25" s="1">
-        <v>-0.00026135917427633736</v>
+        <v>-0.00026140331547696172</v>
       </c>
       <c r="H25" s="1">
-        <v>0.00022271922939599251</v>
+        <v>0.00022511645484702536</v>
       </c>
       <c r="I25" s="1">
-        <v>4.7063208081767277e-06</v>
+        <v>6.7206320466746449e-06</v>
       </c>
       <c r="J25" s="1">
-        <v>-0.0003537630662279605</v>
+        <v>-0.00035348041078906225</v>
       </c>
       <c r="K25" s="1">
-        <v>-0.00020017749659223029</v>
+        <v>-0.00020003549311915485</v>
       </c>
       <c r="L25" s="1">
-        <v>0.00026314914437211876</v>
+        <v>0.00026304739543073501</v>
       </c>
       <c r="M25" s="1">
-        <v>8.2996413472358744e-05</v>
+        <v>8.5366144347252679e-05</v>
       </c>
       <c r="N25" s="1">
-        <v>0.00013911857936758836</v>
+        <v>0.00014074932097476645</v>
       </c>
       <c r="O25" s="1">
-        <v>-9.1050100564592804e-05</v>
+        <v>-8.9342914562707371e-05</v>
       </c>
       <c r="P25" s="1">
-        <v>3.8059782892766101e-05</v>
+        <v>4.0393883376968611e-05</v>
       </c>
       <c r="Q25" s="1">
-        <v>-3.9133756307044233e-05</v>
+        <v>-3.9273264754122747e-05</v>
       </c>
       <c r="R25" s="1">
-        <v>0.00011725711972378135</v>
+        <v>0.00011738693263587486</v>
       </c>
       <c r="S25" s="1">
-        <v>-3.2969213911123721e-05</v>
+        <v>-3.3204122728909286e-05</v>
       </c>
       <c r="T25" s="1">
-        <v>-4.9164895277617211e-05</v>
+        <v>-4.9143908134775252e-05</v>
       </c>
       <c r="U25" s="1">
-        <v>0.00020545198786285846</v>
+        <v>0.00020550543764172378</v>
       </c>
       <c r="V25" s="1">
-        <v>-0.00015321791538404719</v>
+        <v>-0.00015284062817122655</v>
       </c>
       <c r="W25" s="1">
-        <v>0.0013745225970127901</v>
+        <v>0.0013745221907014776</v>
       </c>
       <c r="X25" s="1">
-        <v>0.0014049456939183788</v>
+        <v>0.001404971446223182</v>
       </c>
       <c r="Y25" s="1">
-        <v>0.0013649968172642481</v>
+        <v>0.0013648891338309563</v>
       </c>
       <c r="Z25" s="1">
-        <v>0.0020987644467194556</v>
+        <v>0.0020988950963263739</v>
       </c>
       <c r="AA25" s="1">
-        <v>-2.753040202291041e-05</v>
+        <v>-2.7518662517736235e-05</v>
       </c>
       <c r="AB25" s="1">
-        <v>0.00018257791111066696</v>
+        <v>0.00018226833797690126</v>
       </c>
       <c r="AC25" s="1">
-        <v>0.00047045620804290491</v>
+        <v>0.00047051728181940169</v>
       </c>
       <c r="AD25" s="1">
-        <v>-0.011567121739988287</v>
+        <v>-0.011576520522966748</v>
       </c>
     </row>
     <row r="26">
@@ -4386,91 +4386,91 @@
         <v>56</v>
       </c>
       <c r="B26" s="1">
-        <v>0.030394310007847012</v>
+        <v>0.030406178988485515</v>
       </c>
       <c r="C26" s="1">
-        <v>3.0703270238637221e-05</v>
+        <v>3.0697361751528114e-05</v>
       </c>
       <c r="D26" s="1">
-        <v>-2.9222324530963489e-05</v>
+        <v>-2.9162967033968638e-05</v>
       </c>
       <c r="E26" s="1">
-        <v>2.2397388846689137e-07</v>
+        <v>2.2345195283460088e-07</v>
       </c>
       <c r="F26" s="1">
-        <v>-4.1469965185513902e-05</v>
+        <v>-4.1502926154004952e-05</v>
       </c>
       <c r="G26" s="1">
-        <v>-2.3702041378156772e-05</v>
+        <v>-2.3704785514092833e-05</v>
       </c>
       <c r="H26" s="1">
-        <v>1.1864831868659847e-05</v>
+        <v>1.2157059467935861e-05</v>
       </c>
       <c r="I26" s="1">
-        <v>4.4045655337365065e-05</v>
+        <v>4.4273995539666791e-05</v>
       </c>
       <c r="J26" s="1">
-        <v>3.789383106304176e-05</v>
+        <v>3.7976274810383837e-05</v>
       </c>
       <c r="K26" s="1">
-        <v>4.7795688513482006e-05</v>
+        <v>4.77923895057867e-05</v>
       </c>
       <c r="L26" s="1">
-        <v>-3.2950987603140802e-05</v>
+        <v>-3.3009955384617144e-05</v>
       </c>
       <c r="M26" s="1">
-        <v>2.3884410275531563e-05</v>
+        <v>2.2998047651115298e-05</v>
       </c>
       <c r="N26" s="1">
-        <v>1.0801158396994855e-05</v>
+        <v>1.0429926402464023e-05</v>
       </c>
       <c r="O26" s="1">
-        <v>3.6756876879519278e-05</v>
+        <v>3.6391221582812202e-05</v>
       </c>
       <c r="P26" s="1">
-        <v>3.1826016381666778e-05</v>
+        <v>3.1523376774181322e-05</v>
       </c>
       <c r="Q26" s="1">
-        <v>-4.9745257221354316e-06</v>
+        <v>-5.0478514700682208e-06</v>
       </c>
       <c r="R26" s="1">
-        <v>-1.3059324755440623e-05</v>
+        <v>-1.3012514249033646e-05</v>
       </c>
       <c r="S26" s="1">
-        <v>-9.5435930494038967e-06</v>
+        <v>-9.641698970085761e-06</v>
       </c>
       <c r="T26" s="1">
-        <v>4.2975644553293769e-06</v>
+        <v>4.3237137240494583e-06</v>
       </c>
       <c r="U26" s="1">
-        <v>1.2871512275885922e-05</v>
+        <v>1.2863852309415809e-05</v>
       </c>
       <c r="V26" s="1">
-        <v>-6.6639905679296977e-06</v>
+        <v>-6.6326452828944536e-06</v>
       </c>
       <c r="W26" s="1">
-        <v>-3.5154885553137624e-05</v>
+        <v>-3.5140600144635152e-05</v>
       </c>
       <c r="X26" s="1">
-        <v>-1.9269722479712451e-05</v>
+        <v>-1.9271698944529365e-05</v>
       </c>
       <c r="Y26" s="1">
-        <v>-3.6164782152594287e-05</v>
+        <v>-3.6182728925014593e-05</v>
       </c>
       <c r="Z26" s="1">
-        <v>-2.753040202291041e-05</v>
+        <v>-2.7518662517736235e-05</v>
       </c>
       <c r="AA26" s="1">
-        <v>2.9537698739136896e-05</v>
+        <v>2.9530244435090069e-05</v>
       </c>
       <c r="AB26" s="1">
-        <v>-0.00017058654366539905</v>
+        <v>-0.00017058944475599393</v>
       </c>
       <c r="AC26" s="1">
-        <v>-0.00020270547371484225</v>
+        <v>-0.00020265438645739625</v>
       </c>
       <c r="AD26" s="1">
-        <v>0.00041566508417919602</v>
+        <v>0.00041420025603863331</v>
       </c>
     </row>
     <row r="27">
@@ -4478,91 +4478,91 @@
         <v>57</v>
       </c>
       <c r="B27" s="1">
-        <v>-0.54921268455328498</v>
+        <v>-0.54931216958139806</v>
       </c>
       <c r="C27" s="1">
-        <v>-0.00014938282282643371</v>
+        <v>-0.00014931307563693409</v>
       </c>
       <c r="D27" s="1">
-        <v>0.0002685045399632921</v>
+        <v>0.00026811463243268246</v>
       </c>
       <c r="E27" s="1">
-        <v>-2.0769142357174569e-06</v>
+        <v>-2.0740468800289598e-06</v>
       </c>
       <c r="F27" s="1">
-        <v>0.00010312410555349955</v>
+        <v>0.00010384759538335266</v>
       </c>
       <c r="G27" s="1">
-        <v>6.7344656424772609e-05</v>
+        <v>6.7931593062165591e-05</v>
       </c>
       <c r="H27" s="1">
-        <v>-7.5047214200771447e-05</v>
+        <v>-7.7427768856582163e-05</v>
       </c>
       <c r="I27" s="1">
-        <v>-0.00016184415147045008</v>
+        <v>-0.00016383343116172216</v>
       </c>
       <c r="J27" s="1">
-        <v>-0.00039601807025534087</v>
+        <v>-0.00039614339558507528</v>
       </c>
       <c r="K27" s="1">
-        <v>-0.00015274400946346009</v>
+        <v>-0.00015215913720350964</v>
       </c>
       <c r="L27" s="1">
-        <v>0.00021068570771874207</v>
+        <v>0.00021062266988180849</v>
       </c>
       <c r="M27" s="1">
-        <v>-0.00015704919902300352</v>
+        <v>-0.00015262677757495375</v>
       </c>
       <c r="N27" s="1">
-        <v>-0.0001501203449077006</v>
+        <v>-0.00014831023249386424</v>
       </c>
       <c r="O27" s="1">
-        <v>-0.00027649184603328067</v>
+        <v>-0.0002748439428099617</v>
       </c>
       <c r="P27" s="1">
-        <v>-0.00016244636342382251</v>
+        <v>-0.0001612451690773647</v>
       </c>
       <c r="Q27" s="1">
-        <v>5.1103307073509241e-05</v>
+        <v>5.0658485755169895e-05</v>
       </c>
       <c r="R27" s="1">
-        <v>-1.492716288944854e-05</v>
+        <v>-1.4657399582020635e-05</v>
       </c>
       <c r="S27" s="1">
-        <v>9.1980204965572479e-05</v>
+        <v>9.2372222803047133e-05</v>
       </c>
       <c r="T27" s="1">
-        <v>-2.541767607558594e-05</v>
+        <v>-2.5645370190762948e-05</v>
       </c>
       <c r="U27" s="1">
-        <v>3.357832726139532e-05</v>
+        <v>3.3631820408682508e-05</v>
       </c>
       <c r="V27" s="1">
-        <v>1.5822208045967795e-05</v>
+        <v>1.4673078924287231e-05</v>
       </c>
       <c r="W27" s="1">
-        <v>0.00027587382848206067</v>
+        <v>0.00027565371357394142</v>
       </c>
       <c r="X27" s="1">
-        <v>9.7761048059906886e-05</v>
+        <v>9.7384612483604038e-05</v>
       </c>
       <c r="Y27" s="1">
-        <v>0.00024612535088614342</v>
+        <v>0.0002459935930858883</v>
       </c>
       <c r="Z27" s="1">
-        <v>0.00018257791111066696</v>
+        <v>0.00018226833797690126</v>
       </c>
       <c r="AA27" s="1">
-        <v>-0.00017058654366539905</v>
+        <v>-0.00017058944475599393</v>
       </c>
       <c r="AB27" s="1">
-        <v>0.0038160054916337519</v>
+        <v>0.003815991228627775</v>
       </c>
       <c r="AC27" s="1">
-        <v>0.0014927437346925637</v>
+        <v>0.0014928580640011849</v>
       </c>
       <c r="AD27" s="1">
-        <v>-0.0058182944123433659</v>
+        <v>-0.0058049449573493441</v>
       </c>
     </row>
     <row r="28">
@@ -4570,91 +4570,91 @@
         <v>58</v>
       </c>
       <c r="B28" s="1">
-        <v>-0.30869975888716916</v>
+        <v>-0.30881558744088827</v>
       </c>
       <c r="C28" s="1">
-        <v>0.0002211027817161787</v>
+        <v>0.00022126216367576983</v>
       </c>
       <c r="D28" s="1">
-        <v>0.00083672985607417816</v>
+        <v>0.00083610422314628341</v>
       </c>
       <c r="E28" s="1">
-        <v>-6.8888329484087388e-06</v>
+        <v>-6.8834032390387937e-06</v>
       </c>
       <c r="F28" s="1">
-        <v>-0.00060091668902185168</v>
+        <v>-0.00060060371219394088</v>
       </c>
       <c r="G28" s="1">
-        <v>-0.00079515778733485823</v>
+        <v>-0.0007953618640864149</v>
       </c>
       <c r="H28" s="1">
-        <v>0.00031453555330878086</v>
+        <v>0.00031371494295415994</v>
       </c>
       <c r="I28" s="1">
-        <v>-3.5474930879192705e-05</v>
+        <v>-3.5852264965414039e-05</v>
       </c>
       <c r="J28" s="1">
-        <v>-0.00082130121834357909</v>
+        <v>-0.00082169616808810183</v>
       </c>
       <c r="K28" s="1">
-        <v>-0.00070005291004656496</v>
+        <v>-0.00070035658455277941</v>
       </c>
       <c r="L28" s="1">
-        <v>0.0007668974569817517</v>
+        <v>0.00076717438656892902</v>
       </c>
       <c r="M28" s="1">
-        <v>-0.00023363686829847529</v>
+        <v>-0.00023501872157951839</v>
       </c>
       <c r="N28" s="1">
-        <v>0.00024091415119737727</v>
+        <v>0.00023892831001505531</v>
       </c>
       <c r="O28" s="1">
-        <v>-0.00038342776713306355</v>
+        <v>-0.00038551414231542214</v>
       </c>
       <c r="P28" s="1">
-        <v>-0.00018697354235369093</v>
+        <v>-0.00018937024744497468</v>
       </c>
       <c r="Q28" s="1">
-        <v>0.0001023096100071022</v>
+        <v>0.00010276410766520833</v>
       </c>
       <c r="R28" s="1">
-        <v>0.00064916580668317658</v>
+        <v>0.0006490742623075545</v>
       </c>
       <c r="S28" s="1">
-        <v>-0.00013415981922260643</v>
+        <v>-0.00013325197260220453</v>
       </c>
       <c r="T28" s="1">
-        <v>-0.00013737641915654263</v>
+        <v>-0.0001378291281680117</v>
       </c>
       <c r="U28" s="1">
-        <v>0.00024068360065520895</v>
+        <v>0.00024050821418075772</v>
       </c>
       <c r="V28" s="1">
-        <v>-0.00014268924060088957</v>
+        <v>-0.00014357349765222772</v>
       </c>
       <c r="W28" s="1">
-        <v>9.2553600992713162e-05</v>
+        <v>9.2578720705362529e-05</v>
       </c>
       <c r="X28" s="1">
-        <v>-1.5845446025822838e-05</v>
+        <v>-1.5983978684886943e-05</v>
       </c>
       <c r="Y28" s="1">
-        <v>0.00024967563655823265</v>
+        <v>0.00025019692448735597</v>
       </c>
       <c r="Z28" s="1">
-        <v>0.00047045620804290491</v>
+        <v>0.00047051728181940169</v>
       </c>
       <c r="AA28" s="1">
-        <v>-0.00020270547371484225</v>
+        <v>-0.00020265438645739625</v>
       </c>
       <c r="AB28" s="1">
-        <v>0.0014927437346925637</v>
+        <v>0.0014928580640011849</v>
       </c>
       <c r="AC28" s="1">
-        <v>0.0055992076724508295</v>
+        <v>0.0055996877904761983</v>
       </c>
       <c r="AD28" s="1">
-        <v>-0.022442823665064029</v>
+        <v>-0.022422986824384022</v>
       </c>
     </row>
     <row r="29">
@@ -4662,91 +4662,91 @@
         <v>48</v>
       </c>
       <c r="B29" s="1">
-        <v>-12.771568153094867</v>
+        <v>-12.776207512749334</v>
       </c>
       <c r="C29" s="1">
-        <v>0.019711053348858452</v>
+        <v>0.019721756836726327</v>
       </c>
       <c r="D29" s="1">
-        <v>-0.13177490175099238</v>
+        <v>-0.13175468460728296</v>
       </c>
       <c r="E29" s="1">
-        <v>0.0010574311244198882</v>
+        <v>0.0010572319726645572</v>
       </c>
       <c r="F29" s="1">
-        <v>0.01979925068080483</v>
+        <v>0.019819251177696499</v>
       </c>
       <c r="G29" s="1">
-        <v>0.023950738703727503</v>
+        <v>0.023968867584844549</v>
       </c>
       <c r="H29" s="1">
-        <v>-0.0021186799020329471</v>
+        <v>-0.0021475786777238283</v>
       </c>
       <c r="I29" s="1">
-        <v>-0.0090396172880511782</v>
+        <v>-0.009061612667918037</v>
       </c>
       <c r="J29" s="1">
-        <v>0.039084426417537642</v>
+        <v>0.039111917202489729</v>
       </c>
       <c r="K29" s="1">
-        <v>0.03800647758800986</v>
+        <v>0.038016998220714963</v>
       </c>
       <c r="L29" s="1">
-        <v>-0.031952590189943696</v>
+        <v>-0.031970204997042347</v>
       </c>
       <c r="M29" s="1">
-        <v>-0.001888738302854711</v>
+        <v>-0.0020290847390083333</v>
       </c>
       <c r="N29" s="1">
-        <v>-0.00048640755020138565</v>
+        <v>-0.00057305017629436829</v>
       </c>
       <c r="O29" s="1">
-        <v>0.01202254955694416</v>
+        <v>0.011929009932283569</v>
       </c>
       <c r="P29" s="1">
-        <v>0.0054388672817952885</v>
+        <v>0.0053418272320886369</v>
       </c>
       <c r="Q29" s="1">
-        <v>-0.0078578532581113567</v>
+        <v>-0.0078850728970835185</v>
       </c>
       <c r="R29" s="1">
-        <v>-0.0086988509029209248</v>
+        <v>-0.0086732506916401813</v>
       </c>
       <c r="S29" s="1">
-        <v>0.024348328183547582</v>
+        <v>0.024339460960430971</v>
       </c>
       <c r="T29" s="1">
-        <v>0.02386382796649171</v>
+        <v>0.023855413407898998</v>
       </c>
       <c r="U29" s="1">
-        <v>-0.0016057612810675605</v>
+        <v>-0.001607758475009196</v>
       </c>
       <c r="V29" s="1">
-        <v>0.0040286680793748357</v>
+        <v>0.0039818438517078619</v>
       </c>
       <c r="W29" s="1">
-        <v>-0.010062623184785695</v>
+        <v>-0.010066095472931656</v>
       </c>
       <c r="X29" s="1">
-        <v>-0.0050539260787616867</v>
+        <v>-0.0050614973152840591</v>
       </c>
       <c r="Y29" s="1">
-        <v>-0.011223569844145683</v>
+        <v>-0.01123029636373969</v>
       </c>
       <c r="Z29" s="1">
-        <v>-0.011567121739988287</v>
+        <v>-0.011576520522966748</v>
       </c>
       <c r="AA29" s="1">
-        <v>0.00041566508417919602</v>
+        <v>0.00041420025603863331</v>
       </c>
       <c r="AB29" s="1">
-        <v>-0.0058182944123433659</v>
+        <v>-0.0058049449573493441</v>
       </c>
       <c r="AC29" s="1">
-        <v>-0.022442823665064029</v>
+        <v>-0.022422986824384022</v>
       </c>
       <c r="AD29" s="1">
-        <v>4.0392531114569836</v>
+        <v>4.0388806381053755</v>
       </c>
     </row>
   </sheetData>
